--- a/สูตรคำนวน ANT_สามเหลี่ยม.xlsx
+++ b/สูตรคำนวน ANT_สามเหลี่ยม.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forth\USO-SHF\Maintenance Planning\คู่มืองาน CM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sureerat\Desktop\สูตรคำนวน\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC76DD4-9245-4009-91BD-B5572728F611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E12488-42FD-45DA-97BF-71B39EDE08A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="843" firstSheet="1" activeTab="4" xr2:uid="{5D0D4F63-D4D4-4C8C-977D-010A277C868F}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" tabRatio="843" activeTab="4" xr2:uid="{5D0D4F63-D4D4-4C8C-977D-010A277C868F}"/>
   </bookViews>
   <sheets>
     <sheet name="ข้อกำหนดและการพิจารณา" sheetId="23" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="110">
   <si>
     <t>ความยาวเม้าติ้ง</t>
   </si>
@@ -492,21 +492,89 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve"> ; A = 240, 300 องศา</t>
+    <t>ระยะล่อฟ้าไปหาสายอากาศขา B, C (ค่า C )</t>
   </si>
   <si>
-    <t>ระยะล่อฟ้าไปหาสายอากาศขา B, C (ค่า C )</t>
+    <t>ระยะล่อฟ้าไปหาสายอากาศขา C</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ; A = 120 องศา</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ค่า </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>ค่า</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> b</t>
+    </r>
+  </si>
+  <si>
+    <t>รายการคำนวณระดับความสูงในการติดตั้ง ANT เมื่อขาจับยึดทำมุม 135 องศา กับแนวอ้างอิง</t>
+  </si>
+  <si>
+    <t>รายการคำนวณระดับความสูงในการติดตั้ง ANT เมื่อขาจับยึดทำมุมเดียวกันกับมุมเสาที่มีหน้าตัดสามเหลี่ยม</t>
+  </si>
+  <si>
+    <t>ระยะจากศูนย์กลางสามเหลี่ยมไปยังมุมของเสาแต่ละมุม</t>
+  </si>
+  <si>
+    <t>ระยะจากศูนย์กลางสามเหลี่ยมไปยังตำแหน่งที่ติดตั้งสายอากาศ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="187" formatCode="0.000"/>
     <numFmt numFmtId="188" formatCode="0.0"/>
+    <numFmt numFmtId="189" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -733,6 +801,29 @@
       <sz val="20"/>
       <color rgb="FFFF0000"/>
       <name val="TH Sarabun New"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1535,7 +1626,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1812,6 +1903,94 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="4" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="189" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1857,21 +2036,6 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1881,72 +2045,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="4" fillId="5" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1956,9 +2069,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF00FF"/>
       <color rgb="FF72F927"/>
       <color rgb="FFFFCCFF"/>
-      <color rgb="FFFF00FF"/>
       <color rgb="FFFBFCD0"/>
       <color rgb="FFCC66FF"/>
     </mruColors>
@@ -4966,8 +5079,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9175749" y="2803072"/>
-          <a:ext cx="5990168" cy="1283001"/>
+          <a:off x="9184216" y="2841172"/>
+          <a:ext cx="5998634" cy="1293584"/>
           <a:chOff x="715617" y="1186070"/>
           <a:chExt cx="2902227" cy="1630016"/>
         </a:xfrm>
@@ -5394,8 +5507,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1935839" y="1270964"/>
-          <a:ext cx="3363915" cy="1943347"/>
+          <a:off x="1935839" y="1283664"/>
+          <a:ext cx="3370265" cy="1972980"/>
           <a:chOff x="5620837" y="717743"/>
           <a:chExt cx="2907542" cy="2103801"/>
         </a:xfrm>
@@ -6422,8 +6535,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9397999" y="3598334"/>
-          <a:ext cx="1985131" cy="500442"/>
+          <a:off x="9406466" y="3644901"/>
+          <a:ext cx="1999947" cy="502558"/>
           <a:chOff x="715617" y="1822174"/>
           <a:chExt cx="1543880" cy="337930"/>
         </a:xfrm>
@@ -6579,8 +6692,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8152190" y="4343701"/>
-          <a:ext cx="3230941" cy="837595"/>
+          <a:off x="8160657" y="4392384"/>
+          <a:ext cx="3245757" cy="854529"/>
           <a:chOff x="702365" y="3074504"/>
           <a:chExt cx="1543880" cy="344557"/>
         </a:xfrm>
@@ -7323,7 +7436,7 @@
                       <m:sSup>
                         <m:sSupPr>
                           <m:ctrlPr>
-                            <a:rPr kumimoji="0" lang="th-TH" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+                            <a:rPr kumimoji="0" lang="en-US" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
                               <a:ln>
                                 <a:noFill/>
                               </a:ln>
@@ -7995,7 +8108,7 @@
                       <m:sSup>
                         <m:sSupPr>
                           <m:ctrlPr>
-                            <a:rPr kumimoji="0" lang="th-TH" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+                            <a:rPr kumimoji="0" lang="en-US" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
                               <a:ln>
                                 <a:noFill/>
                               </a:ln>
@@ -9049,8 +9162,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9191143" y="2311015"/>
-          <a:ext cx="5962266" cy="1207462"/>
+          <a:off x="9179598" y="2311015"/>
+          <a:ext cx="5973811" cy="1212080"/>
           <a:chOff x="715617" y="1186070"/>
           <a:chExt cx="2902227" cy="1630016"/>
         </a:xfrm>
@@ -9477,8 +9590,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1941612" y="1294055"/>
-          <a:ext cx="3378347" cy="2118453"/>
+          <a:off x="1936994" y="1294055"/>
+          <a:ext cx="3369110" cy="2123071"/>
           <a:chOff x="5620837" y="717743"/>
           <a:chExt cx="2907542" cy="2103801"/>
         </a:xfrm>
@@ -10505,8 +10618,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9413393" y="3111501"/>
-          <a:ext cx="1986093" cy="420585"/>
+          <a:off x="9401848" y="3116119"/>
+          <a:ext cx="2002256" cy="420585"/>
           <a:chOff x="715617" y="1822174"/>
           <a:chExt cx="1543880" cy="337930"/>
         </a:xfrm>
@@ -10662,8 +10775,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8167584" y="3777011"/>
-          <a:ext cx="3231903" cy="908793"/>
+          <a:off x="8156039" y="3781629"/>
+          <a:ext cx="3248066" cy="908793"/>
           <a:chOff x="702365" y="3074504"/>
           <a:chExt cx="1543880" cy="344557"/>
         </a:xfrm>
@@ -11418,7 +11531,7 @@
                       <m:sSup>
                         <m:sSupPr>
                           <m:ctrlPr>
-                            <a:rPr kumimoji="0" lang="th-TH" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+                            <a:rPr kumimoji="0" lang="en-US" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
                               <a:ln>
                                 <a:noFill/>
                               </a:ln>
@@ -12090,7 +12203,7 @@
                       <m:sSup>
                         <m:sSupPr>
                           <m:ctrlPr>
-                            <a:rPr kumimoji="0" lang="th-TH" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+                            <a:rPr kumimoji="0" lang="en-US" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
                               <a:ln>
                                 <a:noFill/>
                               </a:ln>
@@ -13458,8 +13571,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="17246985" y="2311015"/>
-          <a:ext cx="5959379" cy="1239212"/>
+          <a:off x="17256222" y="2311015"/>
+          <a:ext cx="5968614" cy="1243830"/>
           <a:chOff x="715617" y="1186070"/>
           <a:chExt cx="2902227" cy="1630016"/>
         </a:xfrm>
@@ -13883,8 +13996,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="17500985" y="3111501"/>
-          <a:ext cx="2130410" cy="481059"/>
+          <a:off x="17510222" y="3116119"/>
+          <a:ext cx="2137336" cy="481059"/>
           <a:chOff x="715617" y="1822174"/>
           <a:chExt cx="1543880" cy="337930"/>
         </a:xfrm>
@@ -14040,8 +14153,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="17207675" y="3777011"/>
-          <a:ext cx="2423721" cy="908793"/>
+          <a:off x="17216912" y="3781629"/>
+          <a:ext cx="2430647" cy="908793"/>
           <a:chOff x="702365" y="3074504"/>
           <a:chExt cx="1543880" cy="344557"/>
         </a:xfrm>
@@ -14300,16 +14413,7 @@
                       <a:rPr lang="en-US" sz="1600" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
-                      <m:t>∗(−0.70</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1600" b="0" i="1">
-                        <a:solidFill>
-                          <a:srgbClr val="FF0000"/>
-                        </a:solidFill>
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>8)]=</m:t>
+                      <m:t>∗(−0.708)]=</m:t>
                     </m:r>
                   </m:oMath>
                 </m:oMathPara>
@@ -14897,8 +15001,8 @@
       <xdr:rowOff>52777</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1099457" cy="335480"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -14997,7 +15101,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -15090,8 +15194,8 @@
       <xdr:rowOff>22243</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1088569" cy="336985"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -15190,7 +15294,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -15289,8 +15393,8 @@
       <xdr:rowOff>71387</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1546017" cy="298727"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -15439,7 +15543,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -15576,8 +15680,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9191143" y="2855027"/>
-          <a:ext cx="5994016" cy="1287811"/>
+          <a:off x="9179598" y="2859645"/>
+          <a:ext cx="6005561" cy="1287811"/>
           <a:chOff x="715617" y="1186070"/>
           <a:chExt cx="2902227" cy="1630016"/>
         </a:xfrm>
@@ -15981,502 +16085,18 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1618339</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>254964</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>886504</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>272144</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="13" name="Group 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD115E41-ED5F-4E2A-99DD-8A697C63051D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="1941612" y="1294055"/>
-          <a:ext cx="3378347" cy="1979907"/>
-          <a:chOff x="5620837" y="717743"/>
-          <a:chExt cx="2907542" cy="2103801"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="14" name="Group 13">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1EAD04F-8CA4-4CD9-37A1-2127A9ECCF98}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="5720051" y="717743"/>
-            <a:ext cx="2808328" cy="2103801"/>
-            <a:chOff x="5720051" y="717743"/>
-            <a:chExt cx="2808328" cy="2103801"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="16" name="Right Triangle 15">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{123788FE-0651-3D40-1694-E82A7DE3612C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm flipH="1">
-              <a:off x="5720051" y="717743"/>
-              <a:ext cx="2050969" cy="1439029"/>
-            </a:xfrm>
-            <a:prstGeom prst="rtTriangle">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l"/>
-              <a:endParaRPr lang="th-TH" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-            <xdr:sp macro="" textlink="">
-              <xdr:nvSpPr>
-                <xdr:cNvPr id="17" name="TextBox 16">
-                  <a:extLst>
-                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D796BFB-28C7-AA0A-18AE-46584894757B}"/>
-                    </a:ext>
-                  </a:extLst>
-                </xdr:cNvPr>
-                <xdr:cNvSpPr txBox="1"/>
-              </xdr:nvSpPr>
-              <xdr:spPr>
-                <a:xfrm>
-                  <a:off x="7776511" y="1134836"/>
-                  <a:ext cx="751868" cy="479615"/>
-                </a:xfrm>
-                <a:prstGeom prst="rect">
-                  <a:avLst/>
-                </a:prstGeom>
-                <a:noFill/>
-              </xdr:spPr>
-              <xdr:style>
-                <a:lnRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:lnRef>
-                <a:fillRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:fillRef>
-                <a:effectRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:effectRef>
-                <a:fontRef idx="minor">
-                  <a:schemeClr val="tx1"/>
-                </a:fontRef>
-              </xdr:style>
-              <xdr:txBody>
-                <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-                  <a:noAutofit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr/>
-                  <a14:m>
-                    <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                      <m:oMath>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="2400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑎</m:t>
-                        </m:r>
-                      </m:oMath>
-                    </m:oMathPara>
-                  </a14:m>
-                  <a:endParaRPr lang="th-TH" sz="2400" b="1">
-                    <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                    <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                  </a:endParaRPr>
-                </a:p>
-              </xdr:txBody>
-            </xdr:sp>
-          </mc:Choice>
-          <mc:Fallback>
-            <xdr:sp macro="" textlink="">
-              <xdr:nvSpPr>
-                <xdr:cNvPr id="17" name="TextBox 16">
-                  <a:extLst>
-                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D796BFB-28C7-AA0A-18AE-46584894757B}"/>
-                    </a:ext>
-                  </a:extLst>
-                </xdr:cNvPr>
-                <xdr:cNvSpPr txBox="1"/>
-              </xdr:nvSpPr>
-              <xdr:spPr>
-                <a:xfrm>
-                  <a:off x="7776511" y="1134836"/>
-                  <a:ext cx="751868" cy="479615"/>
-                </a:xfrm>
-                <a:prstGeom prst="rect">
-                  <a:avLst/>
-                </a:prstGeom>
-                <a:noFill/>
-              </xdr:spPr>
-              <xdr:style>
-                <a:lnRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:lnRef>
-                <a:fillRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:fillRef>
-                <a:effectRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:effectRef>
-                <a:fontRef idx="minor">
-                  <a:schemeClr val="tx1"/>
-                </a:fontRef>
-              </xdr:style>
-              <xdr:txBody>
-                <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-                  <a:noAutofit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr/>
-                  <a:r>
-                    <a:rPr lang="en-US" sz="2400" b="0" i="0">
-                      <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                    </a:rPr>
-                    <a:t>𝑎</a:t>
-                  </a:r>
-                  <a:endParaRPr lang="th-TH" sz="2400" b="1">
-                    <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                    <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                  </a:endParaRPr>
-                </a:p>
-              </xdr:txBody>
-            </xdr:sp>
-          </mc:Fallback>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-            <xdr:sp macro="" textlink="">
-              <xdr:nvSpPr>
-                <xdr:cNvPr id="18" name="TextBox 17">
-                  <a:extLst>
-                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2872511C-DC93-2311-C53B-A18BD9336C36}"/>
-                    </a:ext>
-                  </a:extLst>
-                </xdr:cNvPr>
-                <xdr:cNvSpPr txBox="1"/>
-              </xdr:nvSpPr>
-              <xdr:spPr>
-                <a:xfrm>
-                  <a:off x="6173172" y="2341929"/>
-                  <a:ext cx="1470214" cy="479615"/>
-                </a:xfrm>
-                <a:prstGeom prst="rect">
-                  <a:avLst/>
-                </a:prstGeom>
-                <a:noFill/>
-              </xdr:spPr>
-              <xdr:style>
-                <a:lnRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:lnRef>
-                <a:fillRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:fillRef>
-                <a:effectRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:effectRef>
-                <a:fontRef idx="minor">
-                  <a:schemeClr val="tx1"/>
-                </a:fontRef>
-              </xdr:style>
-              <xdr:txBody>
-                <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-                  <a:noAutofit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr/>
-                  <a14:m>
-                    <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                      <m:oMath>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="2400" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑏</m:t>
-                        </m:r>
-                      </m:oMath>
-                    </m:oMathPara>
-                  </a14:m>
-                  <a:endParaRPr lang="th-TH" sz="2400" b="0">
-                    <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                    <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                  </a:endParaRPr>
-                </a:p>
-              </xdr:txBody>
-            </xdr:sp>
-          </mc:Choice>
-          <mc:Fallback>
-            <xdr:sp macro="" textlink="">
-              <xdr:nvSpPr>
-                <xdr:cNvPr id="18" name="TextBox 17">
-                  <a:extLst>
-                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2872511C-DC93-2311-C53B-A18BD9336C36}"/>
-                    </a:ext>
-                  </a:extLst>
-                </xdr:cNvPr>
-                <xdr:cNvSpPr txBox="1"/>
-              </xdr:nvSpPr>
-              <xdr:spPr>
-                <a:xfrm>
-                  <a:off x="6173172" y="2341929"/>
-                  <a:ext cx="1470214" cy="479615"/>
-                </a:xfrm>
-                <a:prstGeom prst="rect">
-                  <a:avLst/>
-                </a:prstGeom>
-                <a:noFill/>
-              </xdr:spPr>
-              <xdr:style>
-                <a:lnRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:lnRef>
-                <a:fillRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:fillRef>
-                <a:effectRef idx="0">
-                  <a:scrgbClr r="0" g="0" b="0"/>
-                </a:effectRef>
-                <a:fontRef idx="minor">
-                  <a:schemeClr val="tx1"/>
-                </a:fontRef>
-              </xdr:style>
-              <xdr:txBody>
-                <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-                  <a:noAutofit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr/>
-                  <a:r>
-                    <a:rPr lang="en-US" sz="2400" b="0" i="0">
-                      <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                    </a:rPr>
-                    <a:t>𝑏</a:t>
-                  </a:r>
-                  <a:endParaRPr lang="th-TH" sz="2400" b="0">
-                    <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                    <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                  </a:endParaRPr>
-                </a:p>
-              </xdr:txBody>
-            </xdr:sp>
-          </mc:Fallback>
-        </mc:AlternateContent>
-      </xdr:grpSp>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-          <xdr:sp macro="" textlink="">
-            <xdr:nvSpPr>
-              <xdr:cNvPr id="15" name="TextBox 14">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D678498-11C7-43C1-A829-B7984558F470}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvSpPr txBox="1"/>
-            </xdr:nvSpPr>
-            <xdr:spPr>
-              <a:xfrm>
-                <a:off x="5620837" y="918634"/>
-                <a:ext cx="1207118" cy="395225"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-              <a:noFill/>
-            </xdr:spPr>
-            <xdr:style>
-              <a:lnRef idx="0">
-                <a:scrgbClr r="0" g="0" b="0"/>
-              </a:lnRef>
-              <a:fillRef idx="0">
-                <a:scrgbClr r="0" g="0" b="0"/>
-              </a:fillRef>
-              <a:effectRef idx="0">
-                <a:scrgbClr r="0" g="0" b="0"/>
-              </a:effectRef>
-              <a:fontRef idx="minor">
-                <a:schemeClr val="tx1"/>
-              </a:fontRef>
-            </xdr:style>
-            <xdr:txBody>
-              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-                <a:noAutofit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr/>
-                <a14:m>
-                  <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:oMath>
-                      <m:r>
-                        <a:rPr lang="en-US" sz="2400" b="0" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        </a:rPr>
-                        <m:t>𝑐</m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="en-US" sz="2400" b="0" i="0">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        </a:rPr>
-                        <m:t>= </m:t>
-                      </m:r>
-                      <m:r>
-                        <a:rPr lang="th-TH" sz="2400" b="0" i="0">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                        </a:rPr>
-                        <m:t>?</m:t>
-                      </m:r>
-                    </m:oMath>
-                  </m:oMathPara>
-                </a14:m>
-                <a:endParaRPr lang="th-TH" sz="2400" b="0">
-                  <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                  <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                </a:endParaRPr>
-              </a:p>
-            </xdr:txBody>
-          </xdr:sp>
-        </mc:Choice>
-        <mc:Fallback>
-          <xdr:sp macro="" textlink="">
-            <xdr:nvSpPr>
-              <xdr:cNvPr id="15" name="TextBox 14">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D678498-11C7-43C1-A829-B7984558F470}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvSpPr txBox="1"/>
-            </xdr:nvSpPr>
-            <xdr:spPr>
-              <a:xfrm>
-                <a:off x="5620837" y="918634"/>
-                <a:ext cx="1207118" cy="395225"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-              <a:noFill/>
-            </xdr:spPr>
-            <xdr:style>
-              <a:lnRef idx="0">
-                <a:scrgbClr r="0" g="0" b="0"/>
-              </a:lnRef>
-              <a:fillRef idx="0">
-                <a:scrgbClr r="0" g="0" b="0"/>
-              </a:fillRef>
-              <a:effectRef idx="0">
-                <a:scrgbClr r="0" g="0" b="0"/>
-              </a:effectRef>
-              <a:fontRef idx="minor">
-                <a:schemeClr val="tx1"/>
-              </a:fontRef>
-            </xdr:style>
-            <xdr:txBody>
-              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-                <a:noAutofit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr/>
-                <a:r>
-                  <a:rPr lang="en-US" sz="2400" b="0" i="0">
-                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  </a:rPr>
-                  <a:t>𝑐= </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="th-TH" sz="2400" b="0" i="0">
-                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                  </a:rPr>
-                  <a:t>?</a:t>
-                </a:r>
-                <a:endParaRPr lang="th-TH" sz="2400" b="0">
-                  <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                  <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-                </a:endParaRPr>
-              </a:p>
-            </xdr:txBody>
-          </xdr:sp>
-        </mc:Fallback>
-      </mc:AlternateContent>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>195944</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>130630</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>183108</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="TextBox 18">
@@ -16542,7 +16162,7 @@
                     <a:rPr lang="en-US" sz="1400" b="0" i="1">
                       <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                     </a:rPr>
-                    <m:t>𝑎</m:t>
+                    <m:t>𝑚</m:t>
                   </m:r>
                   <m:r>
                     <a:rPr lang="en-US" sz="1400" b="0" i="1">
@@ -16567,7 +16187,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="TextBox 18">
@@ -16619,7 +16239,7 @@
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>𝑀𝑜𝑢𝑛𝑡𝑖𝑛𝑔 𝑎 </a:t>
+                <a:t>𝑀𝑜𝑢𝑛𝑡𝑖𝑛𝑔 𝑚 </a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="en-US" sz="2400" b="0">
@@ -16643,17 +16263,17 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>76202</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>10887</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>10888</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>10886</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="20" name="TextBox 19">
@@ -16713,7 +16333,7 @@
                     <a:rPr lang="en-US" sz="1400" b="0" i="1">
                       <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                     </a:rPr>
-                    <m:t>𝑏</m:t>
+                    <m:t>𝐿</m:t>
                   </m:r>
                   <m:r>
                     <a:rPr lang="en-US" sz="1400" b="0" i="1">
@@ -16738,7 +16358,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="20" name="TextBox 19">
@@ -16790,7 +16410,7 @@
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t> 𝑏 </a:t>
+                <a:t> 𝐿 </a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="en-US" sz="2400" b="0">
@@ -16814,17 +16434,17 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>805546</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>21775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>97973</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>76202</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="TextBox 20">
@@ -16922,7 +16542,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="21" name="TextBox 20">
@@ -16974,19 +16594,7 @@
                 <a:rPr lang="en-US" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t> 𝑐</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="th-TH" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>^</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1400" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>2</a:t>
+                <a:t> 𝑐^2</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="en-US" sz="2400" b="0">
@@ -17032,8 +16640,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9413393" y="3665683"/>
-          <a:ext cx="1986093" cy="489858"/>
+          <a:off x="9401848" y="3670301"/>
+          <a:ext cx="2002256" cy="489858"/>
           <a:chOff x="715617" y="1822174"/>
           <a:chExt cx="1543880" cy="337930"/>
         </a:xfrm>
@@ -17189,8 +16797,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8167584" y="4400466"/>
-          <a:ext cx="3231903" cy="839520"/>
+          <a:off x="8156039" y="4405084"/>
+          <a:ext cx="3248066" cy="839520"/>
           <a:chOff x="702365" y="3074504"/>
           <a:chExt cx="1543880" cy="344557"/>
         </a:xfrm>
@@ -17328,8 +16936,8 @@
       <xdr:rowOff>172657</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="990599" cy="370112"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="30" name="TextBox 29">
@@ -17464,7 +17072,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="30" name="TextBox 29">
@@ -17586,8 +17194,8 @@
       <xdr:rowOff>57727</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2271815" cy="312387"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -17713,7 +17321,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="31" name="TextBox 30">
@@ -17763,16 +17371,28 @@
                 <a:t>[2∗𝑎∗𝑏∗</a:t>
               </a:r>
               <a:r>
+                <a:rPr lang="en-US" sz="1600" b="0" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(−</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1600" b="1" i="0">
                   <a:solidFill>
                     <a:srgbClr val="FF0000"/>
                   </a:solidFill>
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>(−𝟎.𝟓)</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1600" b="0" i="0">
+                <a:t>𝟎.𝟓)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1600" b="1" i="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>]=</a:t>
@@ -17857,8 +17477,8 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>94343</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -17969,7 +17589,7 @@
                       <m:sSup>
                         <m:sSupPr>
                           <m:ctrlPr>
-                            <a:rPr kumimoji="0" lang="th-TH" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+                            <a:rPr kumimoji="0" lang="en-US" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
                               <a:ln>
                                 <a:noFill/>
                               </a:ln>
@@ -18111,7 +17731,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="33" name="TextBox 32">
@@ -18479,8 +18099,8 @@
       <xdr:row>2</xdr:row>
       <xdr:rowOff>103413</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="37" name="TextBox 36">
@@ -18591,7 +18211,7 @@
                       <m:sSup>
                         <m:sSupPr>
                           <m:ctrlPr>
-                            <a:rPr kumimoji="0" lang="th-TH" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+                            <a:rPr kumimoji="0" lang="en-US" sz="2400" b="0" i="1" u="none" strike="noStrike" kern="0" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
                               <a:ln>
                                 <a:noFill/>
                               </a:ln>
@@ -18740,7 +18360,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="37" name="TextBox 36">
@@ -18948,76 +18568,6 @@
         </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1065892</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>83154</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>375251</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>297915</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="TextBox 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EEB6F8B-21C7-4D57-9D4E-F3BDA31304B6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4139292" y="2140554"/>
-          <a:ext cx="655559" cy="449711"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="3600" b="1">
-              <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-              <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-            </a:rPr>
-            <a:t>A</a:t>
-          </a:r>
-          <a:endParaRPr lang="th-TH" sz="3600" b="1">
-            <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-            <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
@@ -19062,6 +18612,2275 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>346363</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>34636</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1951181</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>57727</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="Straight Connector 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57821532-3379-DADE-2164-5EE33D4D2777}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="18853727" y="8636000"/>
+          <a:ext cx="1604818" cy="1062182"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1962727</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>34636</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>588819</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>69272</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="Straight Connector 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C8237D1-FA53-4E9C-877E-5C57AD16E6F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20470091" y="8636000"/>
+          <a:ext cx="1616364" cy="1073727"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1962729</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>11545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1974273</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>46182</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="45" name="Straight Connector 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB68AF03-32D6-462F-93FE-9DD1C9C859CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="20470093" y="7088909"/>
+          <a:ext cx="11544" cy="1558637"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1974273</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>357909</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="450272" cy="678263"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="TextBox 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0234F450-9400-0EEB-D83F-CB9B24D72172}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20481637" y="7827818"/>
+          <a:ext cx="450272" cy="678263"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>x</a:t>
+          </a:r>
+          <a:endParaRPr lang="th-TH" sz="3600" b="1">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1581727</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>265548</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>277090</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>242454</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="68" name="Group 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B256A37-2E62-3A2D-1E28-73D4BEAFFC0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1900382" y="958275"/>
+          <a:ext cx="2796308" cy="2290615"/>
+          <a:chOff x="16105910" y="1143002"/>
+          <a:chExt cx="3636818" cy="2609272"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="49" name="Isosceles Triangle 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5428185-7C75-0599-4A89-E41010E5EC99}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="16105910" y="1143002"/>
+            <a:ext cx="3636818" cy="2609272"/>
+          </a:xfrm>
+          <a:prstGeom prst="triangle">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="th-TH" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="50" name="Straight Connector 49">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53EE34F9-0F56-45B5-A124-CBD9F4FECDB1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="16129000" y="2874818"/>
+            <a:ext cx="1789545" cy="877456"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="53" name="Straight Connector 52">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DD0D401-EEAA-4D24-B4A2-E692C1159E15}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:endCxn id="49" idx="4"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="17895455" y="2874818"/>
+            <a:ext cx="1847273" cy="877456"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="002060"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="56" name="Straight Connector 55">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABA59945-8E8A-4D5B-8D32-1DC70850828A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:endCxn id="49" idx="0"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="17918545" y="1143002"/>
+            <a:ext cx="5774" cy="1743362"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+        <mc:Choice Requires="a14">
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="63" name="TextBox 62">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1562266C-A5D0-4D6B-BE35-DD8D2C6B50BB}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="17606820" y="1581726"/>
+                <a:ext cx="958272" cy="461819"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="tx1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr/>
+                <a14:m>
+                  <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:oMath>
+                      <m:r>
+                        <a:rPr lang="en-US" sz="2400" b="1" i="1">
+                          <a:solidFill>
+                            <a:srgbClr val="FF0000"/>
+                          </a:solidFill>
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                        </a:rPr>
+                        <m:t>𝒙</m:t>
+                      </m:r>
+                    </m:oMath>
+                  </m:oMathPara>
+                </a14:m>
+                <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                  <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                  <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </mc:Choice>
+        <mc:Fallback xmlns="">
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="63" name="TextBox 62">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1562266C-A5D0-4D6B-BE35-DD8D2C6B50BB}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="17606820" y="1581726"/>
+                <a:ext cx="958272" cy="461819"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="tx1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="2400" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FF0000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                  </a:rPr>
+                  <a:t>𝒙</a:t>
+                </a:r>
+                <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                  <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                  <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+        <mc:Choice Requires="a14">
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="64" name="TextBox 63">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B4EAEC4-E4C7-4DAD-9CD0-8498C5CCADD6}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="18195636" y="3244273"/>
+                <a:ext cx="958272" cy="461819"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="tx1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr/>
+                <a14:m>
+                  <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:oMath>
+                      <m:r>
+                        <a:rPr lang="en-US" sz="2400" b="1" i="1">
+                          <a:solidFill>
+                            <a:srgbClr val="FF0000"/>
+                          </a:solidFill>
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                        </a:rPr>
+                        <m:t>𝒙</m:t>
+                      </m:r>
+                    </m:oMath>
+                  </m:oMathPara>
+                </a14:m>
+                <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                  <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                  <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </mc:Choice>
+        <mc:Fallback xmlns="">
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="64" name="TextBox 63">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B4EAEC4-E4C7-4DAD-9CD0-8498C5CCADD6}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="18195636" y="3244273"/>
+                <a:ext cx="958272" cy="461819"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="tx1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="2400" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FF0000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                  </a:rPr>
+                  <a:t>𝒙</a:t>
+                </a:r>
+                <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                  <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                  <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+        <mc:Choice Requires="a14">
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="65" name="TextBox 64">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD70355E-75FF-4372-B550-4D2245693703}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="16648545" y="2863273"/>
+                <a:ext cx="958272" cy="461819"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="tx1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr/>
+                <a14:m>
+                  <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:oMath>
+                      <m:r>
+                        <a:rPr lang="en-US" sz="2400" b="1" i="1">
+                          <a:solidFill>
+                            <a:srgbClr val="FF0000"/>
+                          </a:solidFill>
+                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                        </a:rPr>
+                        <m:t>𝒙</m:t>
+                      </m:r>
+                    </m:oMath>
+                  </m:oMathPara>
+                </a14:m>
+                <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                  <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                  <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </mc:Choice>
+        <mc:Fallback xmlns="">
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="65" name="TextBox 64">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD70355E-75FF-4372-B550-4D2245693703}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="16648545" y="2863273"/>
+                <a:ext cx="958272" cy="461819"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="tx1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr/>
+                <a:r>
+                  <a:rPr lang="en-US" sz="2400" b="1" i="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FF0000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                  </a:rPr>
+                  <a:t>𝒙</a:t>
+                </a:r>
+                <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                  <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                  <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                </a:endParaRPr>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="38" name="TextBox 37">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EEB6F8B-21C7-4D57-9D4E-F3BDA31304B6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="18049255" y="2461518"/>
+            <a:ext cx="660178" cy="445670"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="en-US" sz="2800" b="1">
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:rPr>
+              <a:t>A</a:t>
+            </a:r>
+            <a:endParaRPr lang="th-TH" sz="2800" b="1">
+              <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>225137</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>265548</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2620818</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>173182</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="70" name="Straight Connector 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EBD81BA-EC34-756C-C3CB-6FBBB2F8851F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="49" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3307773" y="958275"/>
+          <a:ext cx="3746500" cy="3325089"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>277090</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>242454</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>173182</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="72" name="Straight Connector 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4744A24A-BB0F-84DF-7A05-04D52F99B324}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="49" idx="4"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4710545" y="3244272"/>
+          <a:ext cx="2355273" cy="1039092"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="002060"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>704272</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>242455</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1858818</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>57727</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="75" name="TextBox 74">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{541D8C5F-8962-4471-ACFC-6321FFE4E3B9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5137727" y="1974273"/>
+              <a:ext cx="1154546" cy="392545"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2400" b="1" i="1">
+                        <a:solidFill>
+                          <a:schemeClr val="accent2">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝒄</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2400" b="1" i="0">
+                        <a:solidFill>
+                          <a:schemeClr val="accent2">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>= </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="th-TH" sz="2400" b="1" i="0">
+                        <a:solidFill>
+                          <a:schemeClr val="accent2">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>?</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="75" name="TextBox 74">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{541D8C5F-8962-4471-ACFC-6321FFE4E3B9}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5137727" y="1974273"/>
+              <a:ext cx="1154546" cy="392545"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="2400" b="1" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝒄= </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="th-TH" sz="2400" b="1" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>?</a:t>
+              </a:r>
+              <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>92366</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>23090</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2066636</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>334817</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="76" name="TextBox 75">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8142A518-3C8E-4884-8940-16A5541ACC36}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="415639" y="1408545"/>
+              <a:ext cx="1974270" cy="311727"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>a</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>x</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=0.5774</m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                        <a:solidFill>
+                          <a:srgbClr val="FF0000"/>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>L</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="th-TH" sz="2000" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="76" name="TextBox 75">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8142A518-3C8E-4884-8940-16A5541ACC36}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="415639" y="1408545"/>
+              <a:ext cx="1974270" cy="311727"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="0" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FF0000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>a=x=0.5774L</a:t>
+              </a:r>
+              <a:endParaRPr lang="th-TH" sz="2000" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1662546</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>242455</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2401784</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>69784</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="77" name="TextBox 76">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEA7953E-1074-45F5-98D2-895649916CE4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1985819" y="1974273"/>
+              <a:ext cx="739238" cy="404602"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2400" b="1" i="1">
+                        <a:solidFill>
+                          <a:srgbClr val="FF00FF"/>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                      </a:rPr>
+                      <m:t>𝑳</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF00FF"/>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="77" name="TextBox 76">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEA7953E-1074-45F5-98D2-895649916CE4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1985819" y="1974273"/>
+              <a:ext cx="739238" cy="404602"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="2400" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FF00FF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                </a:rPr>
+                <a:t>𝑳</a:t>
+              </a:r>
+              <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF00FF"/>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>738910</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>184728</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>127329</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>127512</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="79" name="TextBox 78">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D053C670-11BF-4CE1-BEC7-B561AE4B50D2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3821546" y="1916546"/>
+              <a:ext cx="739238" cy="520057"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2400" b="1" i="1">
+                        <a:solidFill>
+                          <a:srgbClr val="FF00FF"/>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                      </a:rPr>
+                      <m:t>𝑳</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF00FF"/>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="79" name="TextBox 78">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D053C670-11BF-4CE1-BEC7-B561AE4B50D2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3821546" y="1916546"/>
+              <a:ext cx="739238" cy="520057"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="2400" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FF00FF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                </a:rPr>
+                <a:t>𝑳</a:t>
+              </a:r>
+              <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF00FF"/>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2493818</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>254000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>473693</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>312239</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="80" name="TextBox 79">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B5F3AC6-D035-4207-9EAC-E15889ABC97D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2817091" y="2909455"/>
+              <a:ext cx="739238" cy="404602"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2400" b="1" i="1">
+                        <a:solidFill>
+                          <a:srgbClr val="FF00FF"/>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                      </a:rPr>
+                      <m:t>𝑳</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF00FF"/>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="80" name="TextBox 79">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B5F3AC6-D035-4207-9EAC-E15889ABC97D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2817091" y="2909455"/>
+              <a:ext cx="739238" cy="404602"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="2400" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="FF00FF"/>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                </a:rPr>
+                <a:t>𝑳</a:t>
+              </a:r>
+              <a:endParaRPr lang="th-TH" sz="2400" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF00FF"/>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>288636</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>11547</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1870364</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>11546</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="81" name="TextBox 80">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3FBD50C-79CA-4EA4-9395-E5B6A4EC5EBB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4722091" y="4121729"/>
+              <a:ext cx="1581728" cy="346362"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="1" i="0">
+                        <a:solidFill>
+                          <a:schemeClr val="accent1">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝐛</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="1" i="0">
+                        <a:solidFill>
+                          <a:schemeClr val="accent1">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>= </m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="1" i="0">
+                        <a:solidFill>
+                          <a:schemeClr val="accent1">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝐚</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="1" i="0">
+                        <a:solidFill>
+                          <a:schemeClr val="accent1">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>+</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="1" i="0">
+                        <a:solidFill>
+                          <a:schemeClr val="accent1">
+                            <a:lumMod val="50000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝐦</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="th-TH" sz="2000" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="81" name="TextBox 80">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3FBD50C-79CA-4EA4-9395-E5B6A4EC5EBB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4722091" y="4121729"/>
+              <a:ext cx="1581728" cy="346362"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="1" i="0">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐛= 𝐚+𝐦</a:t>
+              </a:r>
+              <a:endParaRPr lang="th-TH" sz="2000" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>392546</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>254000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1795127</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>5432</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="84" name="TextBox 83">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C261459-7ADB-494D-8A6C-FB763BBD4CEC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4826001" y="3255818"/>
+              <a:ext cx="1402581" cy="513432"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="2000" b="1" i="0">
+                        <a:solidFill>
+                          <a:srgbClr val="002060"/>
+                        </a:solidFill>
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝐦</m:t>
+                    </m:r>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="th-TH" sz="2000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="002060"/>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="84" name="TextBox 83">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C261459-7ADB-494D-8A6C-FB763BBD4CEC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4826001" y="3255818"/>
+              <a:ext cx="1402581" cy="513432"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr/>
+              <a:r>
+                <a:rPr lang="en-US" sz="2000" b="1" i="0">
+                  <a:solidFill>
+                    <a:srgbClr val="002060"/>
+                  </a:solidFill>
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐦</a:t>
+              </a:r>
+              <a:endParaRPr lang="th-TH" sz="2000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="002060"/>
+                </a:solidFill>
+                <a:latin typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+                <a:cs typeface="TH Sarabun New" panose="020B0500040200020003" pitchFamily="34" charset="-34"/>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2066636</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>178954</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>196273</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>196273</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="86" name="Straight Arrow Connector 85">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F729DCA-4748-ED25-48E1-B10BE0D676AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="76" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2389909" y="1564409"/>
+          <a:ext cx="889000" cy="363682"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:headEnd type="diamond" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -19738,191 +21557,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11627A19-2ED3-4D96-9E3C-8A0222832B45}">
   <dimension ref="B24:B76"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="28.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="28.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="123" customWidth="1"/>
-    <col min="2" max="2" width="150.33203125" style="123" customWidth="1"/>
-    <col min="3" max="16384" width="8.6640625" style="123"/>
+    <col min="2" max="2" width="150.296875" style="123" customWidth="1"/>
+    <col min="3" max="16384" width="8.69921875" style="123"/>
   </cols>
   <sheetData>
-    <row r="24" spans="2:2" ht="34.5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" ht="34.799999999999997" x14ac:dyDescent="0.25">
       <c r="B24" s="125" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="51.5" customHeight="1" x14ac:dyDescent="3">
+    <row r="25" spans="2:2" ht="51.45" customHeight="1" x14ac:dyDescent="2.5">
       <c r="B25" s="130" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="34.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" ht="34.799999999999997" x14ac:dyDescent="0.25">
       <c r="B26" s="125" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="29" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="123" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="123" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="123" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="123" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" s="123" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" s="123" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="131" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="132" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:2" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="142" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="133" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="2:2" ht="32" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:2" ht="32.4" x14ac:dyDescent="0.25">
       <c r="B38" s="126" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" s="123" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="2:2" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" spans="2:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:2" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="2:2" ht="14.55" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="123" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="123" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" s="123" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="129" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="2:2" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:2" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="124"/>
     </row>
-    <row r="57" spans="2:2" ht="23.5" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="57" spans="2:2" ht="23.55" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B57" s="127"/>
     </row>
-    <row r="58" spans="2:2" ht="43" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:2" ht="43.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="124" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" s="123" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" s="123" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="123" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" s="123" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" s="123" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="65" spans="2:2" ht="29" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" s="123" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="2:2" ht="341" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:2" ht="340.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="128"/>
     </row>
-    <row r="67" spans="2:2" ht="63" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:2" ht="63" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B68" s="124" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="69" spans="2:2" ht="24.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:2" ht="24.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="123" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B71" s="123" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B72" s="123" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B73" s="123" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B74" s="123" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="75" spans="2:2" ht="85.5" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:2" ht="86.4" x14ac:dyDescent="0.25">
       <c r="B75" s="128" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B76" s="123" t="s">
         <v>86</v>
       </c>
@@ -19943,40 +21762,40 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:W39"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="27" x14ac:dyDescent="0.9"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="27" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.9140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="31.9140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="2.83203125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="37.9140625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="8.9140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="5.9140625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="31.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="4.4140625" style="1" customWidth="1"/>
-    <col min="12" max="19" width="8.83203125" style="1"/>
-    <col min="20" max="20" width="15.4140625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="5.69921875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="34.69921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.8984375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="31.8984375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="2.796875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="37.8984375" style="15" customWidth="1"/>
+    <col min="7" max="7" width="8.8984375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="5.8984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="31.69921875" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="4.3984375" style="1" customWidth="1"/>
+    <col min="12" max="19" width="8.796875" style="1"/>
+    <col min="20" max="20" width="15.3984375" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="55" customHeight="1" thickBot="1" x14ac:dyDescent="0.85">
-      <c r="A1" s="174" t="s">
+    <row r="1" spans="1:23" ht="55.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="176" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
+      <c r="K1" s="176"/>
     </row>
-    <row r="2" spans="1:23" s="2" customFormat="1" ht="30.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="2" spans="1:23" s="2" customFormat="1" ht="30.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A2" s="89"/>
       <c r="B2" s="90" t="s">
         <v>7</v>
@@ -19986,18 +21805,18 @@
       </c>
       <c r="D2" s="92"/>
       <c r="E2" s="88"/>
-      <c r="F2" s="169" t="s">
+      <c r="F2" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="170"/>
+      <c r="G2" s="169"/>
       <c r="H2" s="69"/>
-      <c r="I2" s="158" t="s">
+      <c r="I2" s="177" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="159"/>
+      <c r="J2" s="178"/>
       <c r="K2" s="94"/>
     </row>
-    <row r="3" spans="1:23" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="3" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A3" s="63">
         <v>1</v>
       </c>
@@ -20032,7 +21851,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="4" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A4" s="7">
         <v>2</v>
       </c>
@@ -20067,7 +21886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="30.5" thickBot="1" x14ac:dyDescent="1.05">
+    <row r="5" spans="1:23" ht="30.6" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A5" s="7">
         <v>3</v>
       </c>
@@ -20104,7 +21923,7 @@
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.9">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.75">
       <c r="A6" s="7">
         <v>4</v>
       </c>
@@ -20118,8 +21937,8 @@
         <v>30</v>
       </c>
       <c r="E6" s="37"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="161"/>
+      <c r="F6" s="172"/>
+      <c r="G6" s="173"/>
       <c r="H6" s="61"/>
       <c r="I6" s="42" t="s">
         <v>56</v>
@@ -20130,7 +21949,7 @@
       </c>
       <c r="K6" s="58"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.9">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.75">
       <c r="A7" s="7">
         <v>5</v>
       </c>
@@ -20144,14 +21963,14 @@
         <v>31</v>
       </c>
       <c r="E7" s="37"/>
-      <c r="F7" s="173"/>
-      <c r="G7" s="161"/>
+      <c r="F7" s="172"/>
+      <c r="G7" s="173"/>
       <c r="H7" s="61"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="162"/>
+      <c r="I7" s="174"/>
+      <c r="J7" s="175"/>
       <c r="K7" s="58"/>
     </row>
-    <row r="8" spans="1:23" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="8" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A8" s="7">
         <v>6</v>
       </c>
@@ -20165,33 +21984,33 @@
         <v>6</v>
       </c>
       <c r="E8" s="37"/>
-      <c r="F8" s="173"/>
-      <c r="G8" s="161"/>
+      <c r="F8" s="172"/>
+      <c r="G8" s="173"/>
       <c r="H8" s="61"/>
-      <c r="I8" s="160"/>
-      <c r="J8" s="162"/>
+      <c r="I8" s="174"/>
+      <c r="J8" s="175"/>
       <c r="K8" s="58"/>
     </row>
-    <row r="9" spans="1:23" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A9" s="166" t="s">
+    <row r="9" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="A9" s="165" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="167"/>
-      <c r="C9" s="167"/>
-      <c r="D9" s="168"/>
+      <c r="B9" s="166"/>
+      <c r="C9" s="166"/>
+      <c r="D9" s="167"/>
       <c r="E9" s="88"/>
-      <c r="F9" s="169" t="s">
+      <c r="F9" s="168" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="170"/>
+      <c r="G9" s="169"/>
       <c r="H9" s="69"/>
-      <c r="I9" s="171" t="s">
+      <c r="I9" s="170" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="172"/>
+      <c r="J9" s="171"/>
       <c r="K9" s="70"/>
     </row>
-    <row r="10" spans="1:23" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="10" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A10" s="82"/>
       <c r="B10" s="83" t="s">
         <v>5</v>
@@ -20222,7 +22041,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="11" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A11" s="8"/>
       <c r="B11" s="9" t="s">
         <v>90</v>
@@ -20256,7 +22075,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="12" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A12" s="8"/>
       <c r="B12" s="9" t="s">
         <v>93</v>
@@ -20288,7 +22107,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.9">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.75">
       <c r="A13" s="8"/>
       <c r="B13" s="9" t="s">
         <v>94</v>
@@ -20320,7 +22139,7 @@
       </c>
       <c r="K13" s="58"/>
     </row>
-    <row r="14" spans="1:23" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="14" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A14" s="11"/>
       <c r="B14" s="12" t="s">
         <v>95</v>
@@ -20338,18 +22157,18 @@
       <c r="J14" s="36"/>
       <c r="K14" s="59"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.9">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.75">
       <c r="F15" s="4"/>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.9">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.75">
       <c r="C16" s="4" t="s">
         <v>97</v>
       </c>
       <c r="F16" s="4"/>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A17" s="29"/>
       <c r="C17" s="4" t="s">
         <v>96</v>
@@ -20359,68 +22178,68 @@
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.75">
       <c r="G18" s="19"/>
       <c r="H18" s="21"/>
       <c r="I18" s="19"/>
       <c r="J18" s="19"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.75">
       <c r="H19" s="21"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.75">
       <c r="H20" s="21"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.75">
       <c r="H21" s="21"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.75">
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.75">
       <c r="A24" s="29"/>
       <c r="G24" s="19"/>
       <c r="H24" s="21"/>
       <c r="I24" s="19"/>
       <c r="J24" s="19"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.75">
       <c r="H25" s="21"/>
       <c r="J25" s="31"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.75">
       <c r="H26" s="21"/>
       <c r="J26" s="31"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.75">
       <c r="C27" s="32"/>
       <c r="E27" s="21"/>
       <c r="G27" s="33"/>
       <c r="H27" s="21"/>
       <c r="J27" s="31"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.75">
       <c r="C28" s="30"/>
       <c r="E28" s="21"/>
       <c r="F28" s="4"/>
       <c r="H28" s="21"/>
       <c r="J28" s="31"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.75">
       <c r="C29" s="32"/>
       <c r="E29" s="21"/>
       <c r="F29" s="4"/>
       <c r="H29" s="21"/>
       <c r="J29" s="31"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.9">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.75">
       <c r="F30" s="4"/>
       <c r="I30" s="4"/>
     </row>
-    <row r="35" spans="4:12" x14ac:dyDescent="0.9">
+    <row r="35" spans="4:12" x14ac:dyDescent="0.75">
       <c r="L35" s="3"/>
     </row>
-    <row r="39" spans="4:12" x14ac:dyDescent="0.9">
+    <row r="39" spans="4:12" x14ac:dyDescent="0.75">
       <c r="D39" s="16"/>
     </row>
   </sheetData>
@@ -20449,62 +22268,62 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:Y44"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="27" x14ac:dyDescent="0.9"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="27" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="4.1640625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="36.1640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="34.58203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="4.6640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="38.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.58203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="5.1640625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="31.9140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="5.1640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="4.19921875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="36.19921875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.69921875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="34.59765625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.69921875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="38.69921875" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="5.19921875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="31.8984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="5.19921875" style="4" customWidth="1"/>
     <col min="12" max="12" width="14.5" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.1640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="30.4140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.83203125" style="1"/>
+    <col min="13" max="13" width="13.69921875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.19921875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="30.3984375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.796875" style="1"/>
     <col min="17" max="17" width="28" style="1" customWidth="1"/>
     <col min="18" max="18" width="12.5" style="1" customWidth="1"/>
-    <col min="19" max="20" width="8.83203125" style="1"/>
-    <col min="21" max="21" width="17.1640625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="17.83203125" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.83203125" style="1"/>
+    <col min="19" max="20" width="8.796875" style="1"/>
+    <col min="21" max="21" width="17.19921875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="17.796875" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="1" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B1" s="18"/>
     </row>
-    <row r="2" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B2" s="18"/>
     </row>
-    <row r="3" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B3" s="18"/>
     </row>
-    <row r="4" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="4" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B4" s="18"/>
     </row>
-    <row r="5" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="5" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B5" s="18"/>
     </row>
-    <row r="6" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="6" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B6" s="18"/>
     </row>
-    <row r="7" spans="2:13" s="4" customFormat="1" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="7" spans="2:13" s="4" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B7" s="18"/>
     </row>
-    <row r="8" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="8" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="E8" s="43"/>
       <c r="F8" s="15"/>
       <c r="G8" s="41">
         <f>C13*C13</f>
         <v>2.25</v>
       </c>
-      <c r="H8" s="150"/>
-      <c r="J8" s="151">
+      <c r="H8" s="186"/>
+      <c r="J8" s="187">
         <f>G8+G9</f>
         <v>3.69</v>
       </c>
@@ -20512,17 +22331,17 @@
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
     </row>
-    <row r="9" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="9" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="E9" s="43"/>
       <c r="F9" s="15"/>
       <c r="G9" s="41">
         <f>C14*C14</f>
         <v>1.44</v>
       </c>
-      <c r="H9" s="150"/>
-      <c r="J9" s="151"/>
+      <c r="H9" s="186"/>
+      <c r="J9" s="187"/>
     </row>
-    <row r="10" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="10" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="E10" s="43"/>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -20530,7 +22349,7 @@
       <c r="I10" s="20"/>
       <c r="J10" s="43"/>
     </row>
-    <row r="11" spans="2:13" s="19" customFormat="1" ht="33" x14ac:dyDescent="0.9">
+    <row r="11" spans="2:13" s="19" customFormat="1" ht="33" x14ac:dyDescent="0.75">
       <c r="B11" s="39" t="s">
         <v>23</v>
       </c>
@@ -20545,7 +22364,7 @@
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
     </row>
-    <row r="12" spans="2:13" s="19" customFormat="1" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="12" spans="2:13" s="19" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="B12" s="23" t="s">
         <v>10</v>
       </c>
@@ -20559,7 +22378,7 @@
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
     </row>
-    <row r="13" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="13" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B13" s="134"/>
       <c r="C13" s="137">
         <v>1.5</v>
@@ -20576,7 +22395,7 @@
       <c r="I13" s="20"/>
       <c r="J13" s="15"/>
     </row>
-    <row r="14" spans="2:13" s="19" customFormat="1" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="14" spans="2:13" s="19" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="B14" s="134"/>
       <c r="C14" s="138">
         <v>1.2</v>
@@ -20588,7 +22407,7 @@
       <c r="I14" s="20"/>
       <c r="J14" s="15"/>
     </row>
-    <row r="15" spans="2:13" s="19" customFormat="1" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="15" spans="2:13" s="19" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="B15" s="25"/>
       <c r="C15" s="136" t="s">
         <v>15</v>
@@ -20600,7 +22419,7 @@
       <c r="I15" s="20"/>
       <c r="J15" s="15"/>
     </row>
-    <row r="16" spans="2:13" s="4" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="16" spans="2:13" s="4" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="B16" s="24" t="s">
         <v>28</v>
       </c>
@@ -20620,8 +22439,8 @@
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
     </row>
-    <row r="17" spans="1:25" s="4" customFormat="1" ht="27.65" customHeight="1" x14ac:dyDescent="0.9"/>
-    <row r="18" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="17" spans="1:25" s="4" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.75"/>
+    <row r="18" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A18" s="1"/>
       <c r="B18" s="17"/>
       <c r="C18" s="1"/>
@@ -20638,27 +22457,27 @@
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
     </row>
-    <row r="19" spans="1:25" ht="39" thickBot="1" x14ac:dyDescent="1.3">
-      <c r="A19" s="155" t="s">
+    <row r="19" spans="1:25" ht="39" thickBot="1" x14ac:dyDescent="1.1000000000000001">
+      <c r="A19" s="191" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="155"/>
-      <c r="C19" s="155"/>
-      <c r="D19" s="155"/>
-      <c r="E19" s="155"/>
-      <c r="F19" s="155"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="155"/>
-      <c r="I19" s="155"/>
-      <c r="J19" s="155"/>
-      <c r="K19" s="155"/>
+      <c r="B19" s="191"/>
+      <c r="C19" s="191"/>
+      <c r="D19" s="191"/>
+      <c r="E19" s="191"/>
+      <c r="F19" s="191"/>
+      <c r="G19" s="191"/>
+      <c r="H19" s="191"/>
+      <c r="I19" s="191"/>
+      <c r="J19" s="191"/>
+      <c r="K19" s="191"/>
       <c r="L19" s="1"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="5"/>
     </row>
-    <row r="20" spans="1:25" s="2" customFormat="1" ht="30.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="20" spans="1:25" s="2" customFormat="1" ht="30.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A20" s="66"/>
       <c r="B20" s="67" t="s">
         <v>7</v>
@@ -20668,15 +22487,15 @@
       </c>
       <c r="D20" s="71"/>
       <c r="E20" s="49"/>
-      <c r="F20" s="152" t="s">
+      <c r="F20" s="188" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="153"/>
+      <c r="G20" s="189"/>
       <c r="H20" s="69"/>
-      <c r="I20" s="154" t="s">
+      <c r="I20" s="190" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="154"/>
+      <c r="J20" s="190"/>
       <c r="K20" s="70"/>
       <c r="L20" s="1"/>
       <c r="V20" s="4"/>
@@ -20684,7 +22503,7 @@
       <c r="X20" s="4"/>
       <c r="Y20" s="6"/>
     </row>
-    <row r="21" spans="1:25" ht="30.5" thickBot="1" x14ac:dyDescent="1.05">
+    <row r="21" spans="1:25" ht="30.6" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A21" s="63">
         <v>1</v>
       </c>
@@ -20724,7 +22543,7 @@
       <c r="X21" s="4"/>
       <c r="Y21" s="5"/>
     </row>
-    <row r="22" spans="1:25" ht="30.5" thickBot="1" x14ac:dyDescent="1.05">
+    <row r="22" spans="1:25" ht="30.6" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A22" s="7">
         <v>2</v>
       </c>
@@ -20765,7 +22584,7 @@
       <c r="X22" s="4"/>
       <c r="Y22" s="5"/>
     </row>
-    <row r="23" spans="1:25" ht="30.5" thickBot="1" x14ac:dyDescent="1.05">
+    <row r="23" spans="1:25" ht="30.6" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A23" s="55">
         <v>3</v>
       </c>
@@ -20803,7 +22622,7 @@
       <c r="X23" s="5"/>
       <c r="Y23" s="5"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.9">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.75">
       <c r="A24" s="55">
         <v>4</v>
       </c>
@@ -20817,8 +22636,8 @@
         <v>30</v>
       </c>
       <c r="E24" s="50"/>
-      <c r="F24" s="160"/>
-      <c r="G24" s="161"/>
+      <c r="F24" s="174"/>
+      <c r="G24" s="173"/>
       <c r="H24" s="61"/>
       <c r="I24" s="42" t="s">
         <v>56</v>
@@ -20830,7 +22649,7 @@
       <c r="K24" s="58"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="25" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A25" s="55">
         <v>5</v>
       </c>
@@ -20844,49 +22663,49 @@
         <v>31</v>
       </c>
       <c r="E25" s="50"/>
-      <c r="F25" s="160"/>
-      <c r="G25" s="161"/>
+      <c r="F25" s="174"/>
+      <c r="G25" s="173"/>
       <c r="H25" s="61"/>
-      <c r="I25" s="160"/>
-      <c r="J25" s="162"/>
+      <c r="I25" s="174"/>
+      <c r="J25" s="175"/>
       <c r="K25" s="58"/>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="26" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A26" s="77"/>
       <c r="B26" s="78"/>
       <c r="C26" s="139"/>
       <c r="D26" s="104"/>
       <c r="E26" s="79"/>
-      <c r="F26" s="163"/>
-      <c r="G26" s="164"/>
+      <c r="F26" s="194"/>
+      <c r="G26" s="195"/>
       <c r="H26" s="80"/>
-      <c r="I26" s="163"/>
-      <c r="J26" s="165"/>
+      <c r="I26" s="194"/>
+      <c r="J26" s="196"/>
       <c r="K26" s="81"/>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A27" s="147" t="s">
+    <row r="27" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="A27" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="148"/>
-      <c r="C27" s="148"/>
-      <c r="D27" s="149"/>
+      <c r="B27" s="184"/>
+      <c r="C27" s="184"/>
+      <c r="D27" s="185"/>
       <c r="E27" s="68"/>
-      <c r="F27" s="156" t="s">
+      <c r="F27" s="192" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="157"/>
+      <c r="G27" s="193"/>
       <c r="H27" s="69"/>
-      <c r="I27" s="158" t="s">
+      <c r="I27" s="177" t="s">
         <v>14</v>
       </c>
-      <c r="J27" s="159"/>
+      <c r="J27" s="178"/>
       <c r="K27" s="70"/>
       <c r="L27" s="1"/>
     </row>
-    <row r="28" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="28" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A28" s="82"/>
       <c r="B28" s="83" t="s">
         <v>5</v>
@@ -20896,10 +22715,10 @@
       </c>
       <c r="D28" s="108"/>
       <c r="E28" s="84"/>
-      <c r="F28" s="143" t="s">
+      <c r="F28" s="179" t="s">
         <v>41</v>
       </c>
-      <c r="G28" s="144"/>
+      <c r="G28" s="180"/>
       <c r="H28" s="65" t="s">
         <v>16</v>
       </c>
@@ -20915,7 +22734,7 @@
       </c>
       <c r="L28" s="1"/>
     </row>
-    <row r="29" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="29" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A29" s="8"/>
       <c r="B29" s="9" t="s">
         <v>90</v>
@@ -20928,8 +22747,8 @@
         <v>21</v>
       </c>
       <c r="E29" s="51"/>
-      <c r="F29" s="143"/>
-      <c r="G29" s="144"/>
+      <c r="F29" s="179"/>
+      <c r="G29" s="180"/>
       <c r="H29" s="57" t="s">
         <v>17</v>
       </c>
@@ -20945,7 +22764,7 @@
       </c>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="30" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A30" s="8"/>
       <c r="B30" s="9" t="s">
         <v>93</v>
@@ -20956,8 +22775,8 @@
       </c>
       <c r="D30" s="74"/>
       <c r="E30" s="51"/>
-      <c r="F30" s="143"/>
-      <c r="G30" s="144"/>
+      <c r="F30" s="179"/>
+      <c r="G30" s="180"/>
       <c r="H30" s="57" t="s">
         <v>9</v>
       </c>
@@ -20973,7 +22792,7 @@
       </c>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.9">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.75">
       <c r="A31" s="8"/>
       <c r="B31" s="9" t="s">
         <v>94</v>
@@ -20986,8 +22805,8 @@
         <v>8</v>
       </c>
       <c r="E31" s="51"/>
-      <c r="F31" s="143"/>
-      <c r="G31" s="144"/>
+      <c r="F31" s="179"/>
+      <c r="G31" s="180"/>
       <c r="H31" s="57" t="s">
         <v>19</v>
       </c>
@@ -21001,7 +22820,7 @@
       <c r="K31" s="58"/>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="32" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A32" s="11"/>
       <c r="B32" s="12" t="s">
         <v>95</v>
@@ -21012,21 +22831,21 @@
       </c>
       <c r="D32" s="75"/>
       <c r="E32" s="52"/>
-      <c r="F32" s="145"/>
-      <c r="G32" s="146"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="182"/>
       <c r="H32" s="62"/>
       <c r="I32" s="48"/>
       <c r="J32" s="36"/>
       <c r="K32" s="59"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="33" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F33" s="4"/>
       <c r="I33" s="4"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.75">
       <c r="C34" s="4" t="s">
         <v>97</v>
       </c>
@@ -21035,7 +22854,7 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.75">
       <c r="C35" s="4" t="s">
         <v>96</v>
       </c>
@@ -21044,23 +22863,23 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F37" s="4"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F38" s="4"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F40" s="4"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F42" s="4"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F44" s="4"/>
     </row>
   </sheetData>
@@ -21092,56 +22911,56 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:Y44"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="27" x14ac:dyDescent="0.9"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="27" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="4.1640625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="36.1640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="34.58203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="4.6640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="38.6640625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="11.58203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="5.1640625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="31.9140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="5.1640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="4.19921875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="36.19921875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.69921875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="34.59765625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.69921875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="38.69921875" style="15" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="5.19921875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="31.8984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="5.19921875" style="4" customWidth="1"/>
     <col min="12" max="12" width="14.5" style="4" customWidth="1"/>
-    <col min="13" max="13" width="26.33203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.1640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="25.58203125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.83203125" style="1"/>
-    <col min="17" max="17" width="11.1640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="26.296875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.19921875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="25.59765625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.796875" style="1"/>
+    <col min="17" max="17" width="11.19921875" style="1" customWidth="1"/>
     <col min="18" max="18" width="6.5" style="1" customWidth="1"/>
-    <col min="19" max="20" width="8.83203125" style="1"/>
-    <col min="21" max="21" width="17.1640625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="17.83203125" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.83203125" style="1"/>
+    <col min="19" max="20" width="8.796875" style="1"/>
+    <col min="21" max="21" width="17.19921875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="17.796875" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="1" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B1" s="18"/>
     </row>
-    <row r="2" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B2" s="18"/>
     </row>
-    <row r="3" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B3" s="18"/>
     </row>
-    <row r="4" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="4" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B4" s="18"/>
     </row>
-    <row r="5" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="5" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B5" s="18"/>
     </row>
-    <row r="6" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="6" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B6" s="18"/>
       <c r="F6" s="15"/>
       <c r="G6" s="41">
         <f>C13*C13</f>
         <v>2.25</v>
       </c>
-      <c r="H6" s="150"/>
-      <c r="J6" s="151">
+      <c r="H6" s="186"/>
+      <c r="J6" s="187">
         <f>G6+G7</f>
         <v>3.69</v>
       </c>
@@ -21151,35 +22970,35 @@
         <f>G6</f>
         <v>2.25</v>
       </c>
-      <c r="O6" s="150"/>
-      <c r="Q6" s="151">
+      <c r="O6" s="186"/>
+      <c r="Q6" s="187">
         <f>N6+N7</f>
         <v>5.13</v>
       </c>
       <c r="R6" s="19"/>
     </row>
-    <row r="7" spans="2:18" s="4" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="7" spans="2:18" s="4" customFormat="1" ht="29.55" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B7" s="18"/>
       <c r="F7" s="15"/>
       <c r="G7" s="41">
         <f>C14*C14</f>
         <v>1.44</v>
       </c>
-      <c r="H7" s="150"/>
+      <c r="H7" s="186"/>
       <c r="I7" s="19"/>
-      <c r="J7" s="151"/>
+      <c r="J7" s="187"/>
       <c r="K7" s="19"/>
       <c r="M7" s="15"/>
       <c r="N7" s="41">
         <f>2*G7</f>
         <v>2.88</v>
       </c>
-      <c r="O7" s="150"/>
+      <c r="O7" s="186"/>
       <c r="P7" s="19"/>
-      <c r="Q7" s="151"/>
+      <c r="Q7" s="187"/>
       <c r="R7" s="19"/>
     </row>
-    <row r="8" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="8" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="E8" s="43"/>
       <c r="F8" s="15"/>
       <c r="G8" s="20"/>
@@ -21193,7 +23012,7 @@
       <c r="P8" s="20"/>
       <c r="Q8" s="43"/>
     </row>
-    <row r="9" spans="2:18" s="19" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="9" spans="2:18" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="E9" s="43"/>
       <c r="F9" s="15"/>
       <c r="G9" s="40">
@@ -21213,7 +23032,7 @@
       <c r="P9" s="15"/>
       <c r="Q9" s="15"/>
     </row>
-    <row r="10" spans="2:18" s="19" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="10" spans="2:18" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="E10" s="43"/>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -21227,7 +23046,7 @@
       <c r="P10" s="15"/>
       <c r="Q10" s="15"/>
     </row>
-    <row r="11" spans="2:18" s="19" customFormat="1" ht="33" x14ac:dyDescent="0.9">
+    <row r="11" spans="2:18" s="19" customFormat="1" ht="33" x14ac:dyDescent="0.75">
       <c r="B11" s="39" t="s">
         <v>23</v>
       </c>
@@ -21255,7 +23074,7 @@
       <c r="P11" s="20"/>
       <c r="Q11" s="15"/>
     </row>
-    <row r="12" spans="2:18" s="19" customFormat="1" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="12" spans="2:18" s="19" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="B12" s="23" t="s">
         <v>10</v>
       </c>
@@ -21275,7 +23094,7 @@
       <c r="P12" s="20"/>
       <c r="Q12" s="15"/>
     </row>
-    <row r="13" spans="2:18" s="19" customFormat="1" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="13" spans="2:18" s="19" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="B13" s="134"/>
       <c r="C13" s="137">
         <v>1.5</v>
@@ -21293,7 +23112,7 @@
       <c r="P13" s="20"/>
       <c r="Q13" s="15"/>
     </row>
-    <row r="14" spans="2:18" s="19" customFormat="1" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="14" spans="2:18" s="19" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="B14" s="134"/>
       <c r="C14" s="138">
         <v>1.2</v>
@@ -21321,13 +23140,13 @@
       <c r="P14" s="15"/>
       <c r="Q14" s="15"/>
     </row>
-    <row r="15" spans="2:18" s="19" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="15" spans="2:18" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B15" s="25"/>
       <c r="C15" s="136" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:18" s="4" customFormat="1" ht="27.65" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="16" spans="2:18" s="4" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B16" s="24" t="s">
         <v>28</v>
       </c>
@@ -21339,8 +23158,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:25" s="4" customFormat="1" ht="27.65" customHeight="1" x14ac:dyDescent="0.9"/>
-    <row r="18" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="17" spans="1:25" s="4" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.75"/>
+    <row r="18" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A18" s="1"/>
       <c r="B18" s="17"/>
       <c r="C18" s="1"/>
@@ -21357,27 +23176,27 @@
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
     </row>
-    <row r="19" spans="1:25" ht="39" thickBot="1" x14ac:dyDescent="1.3">
-      <c r="A19" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="155"/>
-      <c r="C19" s="155"/>
-      <c r="D19" s="155"/>
-      <c r="E19" s="155"/>
-      <c r="F19" s="155"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="155"/>
-      <c r="I19" s="155"/>
-      <c r="J19" s="155"/>
-      <c r="K19" s="155"/>
+    <row r="19" spans="1:25" ht="39" thickBot="1" x14ac:dyDescent="1.1000000000000001">
+      <c r="A19" s="191" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="191"/>
+      <c r="C19" s="191"/>
+      <c r="D19" s="191"/>
+      <c r="E19" s="191"/>
+      <c r="F19" s="191"/>
+      <c r="G19" s="191"/>
+      <c r="H19" s="191"/>
+      <c r="I19" s="191"/>
+      <c r="J19" s="191"/>
+      <c r="K19" s="191"/>
       <c r="L19" s="1"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="5"/>
     </row>
-    <row r="20" spans="1:25" s="2" customFormat="1" ht="30.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="20" spans="1:25" s="2" customFormat="1" ht="30.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A20" s="66"/>
       <c r="B20" s="67" t="s">
         <v>7</v>
@@ -21387,15 +23206,15 @@
       </c>
       <c r="D20" s="71"/>
       <c r="E20" s="49"/>
-      <c r="F20" s="152" t="s">
+      <c r="F20" s="188" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="153"/>
+      <c r="G20" s="189"/>
       <c r="H20" s="69"/>
-      <c r="I20" s="154" t="s">
+      <c r="I20" s="190" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="154"/>
+      <c r="J20" s="190"/>
       <c r="K20" s="70"/>
       <c r="L20" s="1"/>
       <c r="V20" s="4"/>
@@ -21403,7 +23222,7 @@
       <c r="X20" s="4"/>
       <c r="Y20" s="6"/>
     </row>
-    <row r="21" spans="1:25" ht="30.5" thickBot="1" x14ac:dyDescent="1.05">
+    <row r="21" spans="1:25" ht="30.6" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A21" s="63">
         <v>1</v>
       </c>
@@ -21443,7 +23262,7 @@
       <c r="X21" s="4"/>
       <c r="Y21" s="5"/>
     </row>
-    <row r="22" spans="1:25" ht="30.5" thickBot="1" x14ac:dyDescent="1.05">
+    <row r="22" spans="1:25" ht="30.6" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A22" s="7">
         <v>2</v>
       </c>
@@ -21484,7 +23303,7 @@
       <c r="X22" s="4"/>
       <c r="Y22" s="5"/>
     </row>
-    <row r="23" spans="1:25" ht="30.5" thickBot="1" x14ac:dyDescent="1.05">
+    <row r="23" spans="1:25" ht="30.6" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A23" s="55">
         <v>3</v>
       </c>
@@ -21523,7 +23342,7 @@
       <c r="X23" s="5"/>
       <c r="Y23" s="5"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.9">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.75">
       <c r="A24" s="55">
         <v>4</v>
       </c>
@@ -21537,8 +23356,8 @@
         <v>4</v>
       </c>
       <c r="E24" s="50"/>
-      <c r="F24" s="160"/>
-      <c r="G24" s="161"/>
+      <c r="F24" s="174"/>
+      <c r="G24" s="173"/>
       <c r="H24" s="61"/>
       <c r="I24" s="42" t="s">
         <v>56</v>
@@ -21550,7 +23369,7 @@
       <c r="K24" s="58"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.9">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.75">
       <c r="A25" s="55">
         <v>5</v>
       </c>
@@ -21564,15 +23383,15 @@
         <v>30</v>
       </c>
       <c r="E25" s="50"/>
-      <c r="F25" s="160"/>
-      <c r="G25" s="161"/>
+      <c r="F25" s="174"/>
+      <c r="G25" s="173"/>
       <c r="H25" s="61"/>
-      <c r="I25" s="160"/>
-      <c r="J25" s="162"/>
+      <c r="I25" s="174"/>
+      <c r="J25" s="175"/>
       <c r="K25" s="58"/>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="26" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A26" s="77">
         <v>6</v>
       </c>
@@ -21586,35 +23405,35 @@
         <v>31</v>
       </c>
       <c r="E26" s="79"/>
-      <c r="F26" s="163"/>
-      <c r="G26" s="164"/>
+      <c r="F26" s="194"/>
+      <c r="G26" s="195"/>
       <c r="H26" s="80"/>
-      <c r="I26" s="163"/>
-      <c r="J26" s="165"/>
+      <c r="I26" s="194"/>
+      <c r="J26" s="196"/>
       <c r="K26" s="81"/>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A27" s="147" t="s">
+    <row r="27" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="A27" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="148"/>
-      <c r="C27" s="148"/>
-      <c r="D27" s="149"/>
+      <c r="B27" s="184"/>
+      <c r="C27" s="184"/>
+      <c r="D27" s="185"/>
       <c r="E27" s="68"/>
-      <c r="F27" s="158" t="s">
+      <c r="F27" s="177" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="170"/>
+      <c r="G27" s="169"/>
       <c r="H27" s="69"/>
-      <c r="I27" s="158" t="s">
+      <c r="I27" s="177" t="s">
         <v>14</v>
       </c>
-      <c r="J27" s="159"/>
+      <c r="J27" s="178"/>
       <c r="K27" s="70"/>
       <c r="L27" s="1"/>
     </row>
-    <row r="28" spans="1:25" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="28" spans="1:25" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A28" s="82"/>
       <c r="B28" s="83" t="s">
         <v>5</v>
@@ -21646,7 +23465,7 @@
       </c>
       <c r="L28" s="1"/>
     </row>
-    <row r="29" spans="1:25" ht="27.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="29" spans="1:25" ht="27.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A29" s="8"/>
       <c r="B29" s="9" t="s">
         <v>58</v>
@@ -21681,7 +23500,7 @@
       </c>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" spans="1:25" ht="27.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="30" spans="1:25" ht="27.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A30" s="8"/>
       <c r="B30" s="9" t="s">
         <v>59</v>
@@ -21714,7 +23533,7 @@
       </c>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="31" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A31" s="8"/>
       <c r="B31" s="9" t="s">
         <v>60</v>
@@ -21747,7 +23566,7 @@
       <c r="K31" s="58"/>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="1:25" ht="27.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="32" spans="1:25" ht="27.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A32" s="11"/>
       <c r="B32" s="12" t="s">
         <v>61</v>
@@ -21766,13 +23585,13 @@
       <c r="K32" s="59"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="33" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F33" s="4"/>
       <c r="I33" s="4"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.75">
       <c r="C34" s="4" t="s">
         <v>97</v>
       </c>
@@ -21781,7 +23600,7 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.75">
       <c r="C35" s="4" t="s">
         <v>96</v>
       </c>
@@ -21790,23 +23609,23 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F37" s="4"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F38" s="4"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F40" s="4"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F42" s="4"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F44" s="4"/>
     </row>
   </sheetData>
@@ -21839,80 +23658,101 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:Y44"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="27" x14ac:dyDescent="0.9"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="27" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="4.1640625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="36.1640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="34.58203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="4.6640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="38.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.58203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="5.1640625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="31.9140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="5.1640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="4.19921875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="36.19921875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.69921875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="34.59765625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.69921875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="38.69921875" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="5.19921875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="31.8984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="5.19921875" style="4" customWidth="1"/>
     <col min="12" max="12" width="14.5" style="4" customWidth="1"/>
-    <col min="13" max="13" width="13.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.1640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="30.4140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.83203125" style="1"/>
+    <col min="13" max="13" width="13.69921875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.19921875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="30.3984375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.796875" style="1"/>
     <col min="17" max="17" width="28" style="1" customWidth="1"/>
     <col min="18" max="18" width="12.5" style="1" customWidth="1"/>
-    <col min="19" max="20" width="8.83203125" style="1"/>
-    <col min="21" max="21" width="17.1640625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="17.83203125" style="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.83203125" style="1"/>
+    <col min="19" max="20" width="8.796875" style="1"/>
+    <col min="21" max="21" width="17.19921875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="17.796875" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="1" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B1" s="18"/>
     </row>
-    <row r="2" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B2" s="18"/>
     </row>
-    <row r="3" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B3" s="18"/>
+      <c r="F3" s="162"/>
     </row>
-    <row r="4" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="4" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B4" s="18"/>
     </row>
-    <row r="5" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="5" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B5" s="18"/>
+      <c r="F5" s="163" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="143">
+        <f>C12*C15</f>
+        <v>0.69288000000000005</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>108</v>
+      </c>
     </row>
-    <row r="6" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="6" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B6" s="18"/>
+      <c r="F6" s="164" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="143">
+        <f>G5+C14</f>
+        <v>2.1928800000000002</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>109</v>
+      </c>
     </row>
-    <row r="7" spans="2:13" s="4" customFormat="1" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="7" spans="2:13" s="4" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.75">
       <c r="B7" s="18"/>
     </row>
-    <row r="8" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="8" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.75">
       <c r="E8" s="43"/>
       <c r="F8" s="15"/>
       <c r="G8" s="41">
-        <f>C13*C13</f>
-        <v>2.25</v>
-      </c>
-      <c r="H8" s="150"/>
-      <c r="J8" s="151">
+        <f>POWER(G5,2)</f>
+        <v>0.48008269440000007</v>
+      </c>
+      <c r="H8" s="186"/>
+      <c r="J8" s="187">
         <f>G8+G9</f>
-        <v>3.69</v>
+        <v>8.8076934720000022</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
     </row>
-    <row r="9" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="9" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="E9" s="43"/>
       <c r="F9" s="15"/>
       <c r="G9" s="41">
-        <f>C14*C14</f>
-        <v>1.44</v>
-      </c>
-      <c r="H9" s="150"/>
-      <c r="J9" s="151"/>
+        <f>POWER(G5+G6,2)</f>
+        <v>8.3276107776000021</v>
+      </c>
+      <c r="H9" s="186"/>
+      <c r="J9" s="187"/>
     </row>
-    <row r="10" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="10" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="E10" s="43"/>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -21920,7 +23760,7 @@
       <c r="I10" s="20"/>
       <c r="J10" s="43"/>
     </row>
-    <row r="11" spans="2:13" s="19" customFormat="1" ht="33" x14ac:dyDescent="0.9">
+    <row r="11" spans="2:13" s="19" customFormat="1" ht="33" x14ac:dyDescent="0.75">
       <c r="B11" s="39" t="s">
         <v>23</v>
       </c>
@@ -21928,19 +23768,19 @@
       <c r="E11" s="43"/>
       <c r="F11" s="15"/>
       <c r="G11" s="40">
-        <f>C12*C13*C14*C16</f>
-        <v>-1.7999999999999998</v>
+        <f>C13*G5*G6*C17</f>
+        <v>-1.5194026944000003</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
     </row>
-    <row r="12" spans="2:13" s="19" customFormat="1" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="12" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B12" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="135">
-        <v>2</v>
+      <c r="C12" s="161">
+        <v>0.57740000000000002</v>
       </c>
       <c r="E12" s="43"/>
       <c r="F12" s="15"/>
@@ -21949,10 +23789,12 @@
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
     </row>
-    <row r="13" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.9">
-      <c r="B13" s="134"/>
-      <c r="C13" s="137">
-        <v>1.5</v>
+    <row r="13" spans="2:13" s="19" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="B13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="135">
+        <v>2</v>
       </c>
       <c r="E13" s="43"/>
       <c r="F13" s="44" t="s">
@@ -21960,16 +23802,16 @@
       </c>
       <c r="G13" s="40">
         <f>J8-G11</f>
-        <v>5.49</v>
+        <v>10.327096166400002</v>
       </c>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
       <c r="J13" s="15"/>
     </row>
-    <row r="14" spans="2:13" s="19" customFormat="1" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="14" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B14" s="134"/>
-      <c r="C14" s="138">
-        <v>1.2</v>
+      <c r="C14" s="137">
+        <v>1.5</v>
       </c>
       <c r="E14" s="43"/>
       <c r="F14" s="15"/>
@@ -21978,10 +23820,10 @@
       <c r="I14" s="20"/>
       <c r="J14" s="15"/>
     </row>
-    <row r="15" spans="2:13" s="19" customFormat="1" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B15" s="25"/>
-      <c r="C15" s="136" t="s">
-        <v>15</v>
+    <row r="15" spans="2:13" s="19" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="B15" s="134"/>
+      <c r="C15" s="138">
+        <v>1.2</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
@@ -21990,28 +23832,33 @@
       <c r="I15" s="20"/>
       <c r="J15" s="15"/>
     </row>
-    <row r="16" spans="2:13" s="4" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="1.05">
-      <c r="B16" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="95">
-        <v>-0.5</v>
-      </c>
-      <c r="D16" s="175" t="s">
-        <v>101</v>
+    <row r="16" spans="2:13" s="4" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="B16" s="25"/>
+      <c r="C16" s="136" t="s">
+        <v>15</v>
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
       <c r="G16" s="97">
         <f>SQRT(G13)</f>
-        <v>2.3430749027719964</v>
+        <v>3.213579961102571</v>
       </c>
       <c r="H16" s="22"/>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
     </row>
-    <row r="17" spans="1:25" s="4" customFormat="1" ht="27.65" customHeight="1" x14ac:dyDescent="0.9"/>
-    <row r="18" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="17" spans="1:25" s="4" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="B17" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="95">
+        <v>-0.5</v>
+      </c>
+      <c r="D17" s="144" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A18" s="1"/>
       <c r="B18" s="17"/>
       <c r="C18" s="1"/>
@@ -22028,27 +23875,27 @@
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
     </row>
-    <row r="19" spans="1:25" ht="39" thickBot="1" x14ac:dyDescent="1.3">
-      <c r="A19" s="155" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="155"/>
-      <c r="C19" s="155"/>
-      <c r="D19" s="155"/>
-      <c r="E19" s="155"/>
-      <c r="F19" s="155"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="155"/>
-      <c r="I19" s="155"/>
-      <c r="J19" s="155"/>
-      <c r="K19" s="155"/>
+    <row r="19" spans="1:25" ht="39" thickBot="1" x14ac:dyDescent="1.1000000000000001">
+      <c r="A19" s="197" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="198"/>
+      <c r="C19" s="198"/>
+      <c r="D19" s="198"/>
+      <c r="E19" s="198"/>
+      <c r="F19" s="198"/>
+      <c r="G19" s="198"/>
+      <c r="H19" s="198"/>
+      <c r="I19" s="198"/>
+      <c r="J19" s="198"/>
+      <c r="K19" s="199"/>
       <c r="L19" s="1"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="5"/>
     </row>
-    <row r="20" spans="1:25" s="2" customFormat="1" ht="30.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="20" spans="1:25" s="2" customFormat="1" ht="30.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A20" s="66"/>
       <c r="B20" s="67" t="s">
         <v>7</v>
@@ -22057,16 +23904,16 @@
         <v>25</v>
       </c>
       <c r="D20" s="71"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="152" t="s">
+      <c r="E20" s="70"/>
+      <c r="F20" s="188" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="153"/>
+      <c r="G20" s="189"/>
       <c r="H20" s="69"/>
-      <c r="I20" s="154" t="s">
+      <c r="I20" s="190" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="154"/>
+      <c r="J20" s="190"/>
       <c r="K20" s="70"/>
       <c r="L20" s="1"/>
       <c r="V20" s="4"/>
@@ -22074,7 +23921,7 @@
       <c r="X20" s="4"/>
       <c r="Y20" s="6"/>
     </row>
-    <row r="21" spans="1:25" ht="30.5" thickBot="1" x14ac:dyDescent="1.05">
+    <row r="21" spans="1:25" ht="30.6" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A21" s="63">
         <v>1</v>
       </c>
@@ -22087,7 +23934,9 @@
       <c r="D21" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="51"/>
+      <c r="E21" s="65" t="s">
+        <v>16</v>
+      </c>
       <c r="F21" s="64" t="s">
         <v>88</v>
       </c>
@@ -22099,11 +23948,11 @@
         <v>16</v>
       </c>
       <c r="I21" s="76" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J21" s="96">
         <f>$C$22</f>
-        <v>2.3430749027719964</v>
+        <v>3.213579961102571</v>
       </c>
       <c r="K21" s="65" t="s">
         <v>16</v>
@@ -22114,21 +23963,23 @@
       <c r="X21" s="4"/>
       <c r="Y21" s="5"/>
     </row>
-    <row r="22" spans="1:25" ht="30.5" thickBot="1" x14ac:dyDescent="1.05">
+    <row r="22" spans="1:25" ht="30.6" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A22" s="7">
         <v>2</v>
       </c>
       <c r="B22" s="73" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="141">
         <f>G16</f>
-        <v>2.3430749027719964</v>
+        <v>3.213579961102571</v>
       </c>
       <c r="D22" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="51"/>
+      <c r="E22" s="57" t="s">
+        <v>17</v>
+      </c>
       <c r="F22" s="26" t="s">
         <v>89</v>
       </c>
@@ -22144,7 +23995,7 @@
       </c>
       <c r="J22" s="27">
         <f>(J21+($C$24*$C$25))/$C$25</f>
-        <v>6.4930749027719967</v>
+        <v>7.3635799611025714</v>
       </c>
       <c r="K22" s="57" t="s">
         <v>17</v>
@@ -22155,7 +24006,7 @@
       <c r="X22" s="4"/>
       <c r="Y22" s="5"/>
     </row>
-    <row r="23" spans="1:25" ht="30.5" thickBot="1" x14ac:dyDescent="1.05">
+    <row r="23" spans="1:25" ht="30.6" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A23" s="55">
         <v>3</v>
       </c>
@@ -22168,7 +24019,9 @@
       <c r="D23" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="51"/>
+      <c r="E23" s="57" t="s">
+        <v>9</v>
+      </c>
       <c r="F23" s="38" t="s">
         <v>57</v>
       </c>
@@ -22184,7 +24037,7 @@
       </c>
       <c r="J23" s="56">
         <f>J22-$C$21</f>
-        <v>-6.9250972280032741E-3</v>
+        <v>0.8635799611025714</v>
       </c>
       <c r="K23" s="57" t="s">
         <v>9</v>
@@ -22193,7 +24046,7 @@
       <c r="X23" s="5"/>
       <c r="Y23" s="5"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.9">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.75">
       <c r="A24" s="55">
         <v>4</v>
       </c>
@@ -22206,9 +24059,9 @@
       <c r="D24" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="50"/>
-      <c r="F24" s="160"/>
-      <c r="G24" s="161"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="174"/>
+      <c r="G24" s="173"/>
       <c r="H24" s="57" t="s">
         <v>19</v>
       </c>
@@ -22217,12 +24070,12 @@
       </c>
       <c r="J24" s="28">
         <f>$C$28-J23</f>
-        <v>72.006925097228006</v>
+        <v>71.136420038897427</v>
       </c>
       <c r="K24" s="58"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="25" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A25" s="55">
         <v>5</v>
       </c>
@@ -22235,50 +24088,48 @@
       <c r="D25" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="E25" s="50"/>
-      <c r="F25" s="160"/>
-      <c r="G25" s="161"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="174"/>
+      <c r="G25" s="173"/>
       <c r="H25" s="62"/>
       <c r="I25" s="48"/>
       <c r="J25" s="36"/>
       <c r="K25" s="59"/>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="26" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A26" s="77"/>
       <c r="B26" s="78"/>
       <c r="C26" s="139"/>
       <c r="D26" s="104"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="163"/>
-      <c r="G26" s="164"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="194"/>
+      <c r="G26" s="195"/>
       <c r="H26" s="80"/>
-      <c r="I26" s="163"/>
-      <c r="J26" s="165"/>
+      <c r="I26" s="194"/>
+      <c r="J26" s="196"/>
       <c r="K26" s="81"/>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" spans="1:25" ht="27.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="A27" s="147" t="s">
+    <row r="27" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="A27" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="148"/>
-      <c r="C27" s="148"/>
-      <c r="D27" s="149"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="158" t="s">
+      <c r="B27" s="184"/>
+      <c r="C27" s="184"/>
+      <c r="D27" s="185"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="177" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="170"/>
+      <c r="G27" s="169"/>
       <c r="H27" s="69"/>
-      <c r="I27" s="186" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="187"/>
+      <c r="I27" s="200"/>
+      <c r="J27" s="201"/>
       <c r="K27" s="70"/>
       <c r="L27" s="1"/>
     </row>
-    <row r="28" spans="1:25" ht="27.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="28" spans="1:25" ht="27.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A28" s="82"/>
       <c r="B28" s="83" t="s">
         <v>5</v>
@@ -22291,23 +24142,21 @@
         <v>16</v>
       </c>
       <c r="F28" s="76" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="G28" s="96">
         <f>$C$22</f>
-        <v>2.3430749027719964</v>
-      </c>
-      <c r="H28" s="179" t="s">
+        <v>3.213579961102571</v>
+      </c>
+      <c r="H28" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="I28" s="188"/>
-      <c r="J28" s="189"/>
-      <c r="K28" s="183" t="s">
-        <v>16</v>
-      </c>
+      <c r="I28" s="155"/>
+      <c r="J28" s="156"/>
+      <c r="K28" s="152"/>
       <c r="L28" s="1"/>
     </row>
-    <row r="29" spans="1:25" ht="27.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="29" spans="1:25" ht="27.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A29" s="8"/>
       <c r="B29" s="9" t="s">
         <v>90</v>
@@ -22327,26 +24176,24 @@
       </c>
       <c r="G29" s="27">
         <f>(G28+($C$24*$C$25))/$C$25</f>
-        <v>6.4930749027719967</v>
-      </c>
-      <c r="H29" s="180" t="s">
+        <v>7.3635799611025714</v>
+      </c>
+      <c r="H29" s="149" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="190"/>
-      <c r="J29" s="176"/>
-      <c r="K29" s="93" t="s">
-        <v>17</v>
-      </c>
+      <c r="I29" s="157"/>
+      <c r="J29" s="145"/>
+      <c r="K29" s="93"/>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" spans="1:25" ht="27.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="30" spans="1:25" ht="27.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A30" s="8"/>
       <c r="B30" s="9" t="s">
         <v>93</v>
       </c>
       <c r="C30" s="10">
         <f>J23</f>
-        <v>-6.9250972280032741E-3</v>
+        <v>0.8635799611025714</v>
       </c>
       <c r="D30" s="74"/>
       <c r="E30" s="57" t="s">
@@ -22357,26 +24204,24 @@
       </c>
       <c r="G30" s="56">
         <f>G29-$C$21</f>
-        <v>-6.9250972280032741E-3</v>
-      </c>
-      <c r="H30" s="180" t="s">
+        <v>0.8635799611025714</v>
+      </c>
+      <c r="H30" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="I30" s="191"/>
-      <c r="J30" s="193"/>
-      <c r="K30" s="93" t="s">
-        <v>9</v>
-      </c>
+      <c r="I30" s="158"/>
+      <c r="J30" s="160"/>
+      <c r="K30" s="93"/>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="31" spans="1:25" ht="27" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A31" s="8"/>
       <c r="B31" s="9" t="s">
         <v>94</v>
       </c>
       <c r="C31" s="10">
         <f>G31</f>
-        <v>72.006925097228006</v>
+        <v>71.136420038897427</v>
       </c>
       <c r="D31" s="74" t="s">
         <v>8</v>
@@ -22389,15 +24234,15 @@
       </c>
       <c r="G31" s="28">
         <f>$C$28-G30</f>
-        <v>72.006925097228006</v>
-      </c>
-      <c r="H31" s="181"/>
-      <c r="I31" s="190"/>
-      <c r="J31" s="177"/>
-      <c r="K31" s="184"/>
+        <v>71.136420038897427</v>
+      </c>
+      <c r="H31" s="150"/>
+      <c r="I31" s="157"/>
+      <c r="J31" s="146"/>
+      <c r="K31" s="153"/>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="1:25" ht="27.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="32" spans="1:25" ht="27.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A32" s="11"/>
       <c r="B32" s="12" t="s">
         <v>95</v>
@@ -22410,19 +24255,19 @@
       <c r="E32" s="62"/>
       <c r="F32" s="48"/>
       <c r="G32" s="36"/>
-      <c r="H32" s="182"/>
-      <c r="I32" s="192"/>
-      <c r="J32" s="178"/>
-      <c r="K32" s="185"/>
+      <c r="H32" s="151"/>
+      <c r="I32" s="159"/>
+      <c r="J32" s="147"/>
+      <c r="K32" s="154"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="33" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F33" s="4"/>
       <c r="I33" s="4"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.75">
       <c r="C34" s="4" t="s">
         <v>97</v>
       </c>
@@ -22431,7 +24276,7 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.75">
       <c r="C35" s="4" t="s">
         <v>96</v>
       </c>
@@ -22440,39 +24285,39 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F37" s="4"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F38" s="4"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F40" s="4"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F42" s="4"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.9">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.75">
       <c r="F44" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="I27:J27"/>
     <mergeCell ref="H8:H9"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="A19:K19"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="I27:J27"/>
   </mergeCells>
   <pageMargins left="0.37" right="0.17" top="0.37" bottom="0.17" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" orientation="landscape" r:id="rId1"/>
@@ -22483,7 +24328,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35BFAFA-7F3D-4549-9297-4D8AD11E978C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22494,7 +24339,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8578C8D-3361-413F-8BF3-55A76AD90DE1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -22504,7 +24349,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FF3179-2B5E-4B7E-A9D1-0661EA7FA451}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/สูตรคำนวน ANT_สามเหลี่ยม.xlsx
+++ b/สูตรคำนวน ANT_สามเหลี่ยม.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sureerat\Desktop\สูตรคำนวน\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E12488-42FD-45DA-97BF-71B39EDE08A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1885820-48A0-4F1B-A7D9-738B2670F632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" tabRatio="843" activeTab="4" xr2:uid="{5D0D4F63-D4D4-4C8C-977D-010A277C868F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="843" activeTab="4" xr2:uid="{5D0D4F63-D4D4-4C8C-977D-010A277C868F}"/>
   </bookViews>
   <sheets>
     <sheet name="ข้อกำหนดและการพิจารณา" sheetId="23" r:id="rId1"/>
@@ -1949,6 +1949,66 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1961,9 +2021,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1973,19 +2030,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2003,30 +2051,6 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2034,30 +2058,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -15680,8 +15680,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9179598" y="2859645"/>
-          <a:ext cx="6005561" cy="1287811"/>
+          <a:off x="9180587" y="2877458"/>
+          <a:ext cx="5998634" cy="1302655"/>
           <a:chOff x="715617" y="1186070"/>
           <a:chExt cx="2902227" cy="1630016"/>
         </a:xfrm>
@@ -16640,8 +16640,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9401848" y="3670301"/>
-          <a:ext cx="2002256" cy="489858"/>
+          <a:off x="9402837" y="3692072"/>
+          <a:ext cx="1996319" cy="500744"/>
           <a:chOff x="715617" y="1822174"/>
           <a:chExt cx="1543880" cy="337930"/>
         </a:xfrm>
@@ -16797,8 +16797,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8156039" y="4405084"/>
-          <a:ext cx="3248066" cy="839520"/>
+          <a:off x="8157028" y="4437741"/>
+          <a:ext cx="3242129" cy="845458"/>
           <a:chOff x="702365" y="3074504"/>
           <a:chExt cx="1543880" cy="344557"/>
         </a:xfrm>
@@ -18872,8 +18872,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1900382" y="958275"/>
-          <a:ext cx="2796308" cy="2290615"/>
+          <a:off x="1897413" y="962234"/>
+          <a:ext cx="2799277" cy="2306449"/>
           <a:chOff x="16105910" y="1143002"/>
           <a:chExt cx="3636818" cy="2609272"/>
         </a:xfrm>
@@ -21781,19 +21781,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="55.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="193" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="176"/>
-      <c r="K1" s="176"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
     </row>
     <row r="2" spans="1:23" s="2" customFormat="1" ht="30.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A2" s="89"/>
@@ -21805,15 +21805,15 @@
       </c>
       <c r="D2" s="92"/>
       <c r="E2" s="88"/>
-      <c r="F2" s="168" t="s">
+      <c r="F2" s="188" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="169"/>
+      <c r="G2" s="182"/>
       <c r="H2" s="69"/>
-      <c r="I2" s="177" t="s">
+      <c r="I2" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="178"/>
+      <c r="J2" s="194"/>
       <c r="K2" s="94"/>
     </row>
     <row r="3" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
@@ -21937,8 +21937,8 @@
         <v>30</v>
       </c>
       <c r="E6" s="37"/>
-      <c r="F6" s="172"/>
-      <c r="G6" s="173"/>
+      <c r="F6" s="191"/>
+      <c r="G6" s="166"/>
       <c r="H6" s="61"/>
       <c r="I6" s="42" t="s">
         <v>56</v>
@@ -21963,11 +21963,11 @@
         <v>31</v>
       </c>
       <c r="E7" s="37"/>
-      <c r="F7" s="172"/>
-      <c r="G7" s="173"/>
+      <c r="F7" s="191"/>
+      <c r="G7" s="166"/>
       <c r="H7" s="61"/>
-      <c r="I7" s="174"/>
-      <c r="J7" s="175"/>
+      <c r="I7" s="165"/>
+      <c r="J7" s="192"/>
       <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
@@ -21984,30 +21984,30 @@
         <v>6</v>
       </c>
       <c r="E8" s="37"/>
-      <c r="F8" s="172"/>
-      <c r="G8" s="173"/>
+      <c r="F8" s="191"/>
+      <c r="G8" s="166"/>
       <c r="H8" s="61"/>
-      <c r="I8" s="174"/>
-      <c r="J8" s="175"/>
+      <c r="I8" s="165"/>
+      <c r="J8" s="192"/>
       <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
-      <c r="A9" s="165" t="s">
+      <c r="A9" s="185" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="166"/>
-      <c r="C9" s="166"/>
-      <c r="D9" s="167"/>
+      <c r="B9" s="186"/>
+      <c r="C9" s="186"/>
+      <c r="D9" s="187"/>
       <c r="E9" s="88"/>
-      <c r="F9" s="168" t="s">
+      <c r="F9" s="188" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="169"/>
+      <c r="G9" s="182"/>
       <c r="H9" s="69"/>
-      <c r="I9" s="170" t="s">
+      <c r="I9" s="189" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="171"/>
+      <c r="J9" s="190"/>
       <c r="K9" s="70"/>
     </row>
     <row r="10" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
@@ -22322,8 +22322,8 @@
         <f>C13*C13</f>
         <v>2.25</v>
       </c>
-      <c r="H8" s="186"/>
-      <c r="J8" s="187">
+      <c r="H8" s="170"/>
+      <c r="J8" s="171">
         <f>G8+G9</f>
         <v>3.69</v>
       </c>
@@ -22338,8 +22338,8 @@
         <f>C14*C14</f>
         <v>1.44</v>
       </c>
-      <c r="H9" s="186"/>
-      <c r="J9" s="187"/>
+      <c r="H9" s="170"/>
+      <c r="J9" s="171"/>
     </row>
     <row r="10" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="E10" s="43"/>
@@ -22458,19 +22458,19 @@
       <c r="X18" s="4"/>
     </row>
     <row r="19" spans="1:25" ht="39" thickBot="1" x14ac:dyDescent="1.1000000000000001">
-      <c r="A19" s="191" t="s">
+      <c r="A19" s="199" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="191"/>
-      <c r="C19" s="191"/>
-      <c r="D19" s="191"/>
-      <c r="E19" s="191"/>
-      <c r="F19" s="191"/>
-      <c r="G19" s="191"/>
-      <c r="H19" s="191"/>
-      <c r="I19" s="191"/>
-      <c r="J19" s="191"/>
-      <c r="K19" s="191"/>
+      <c r="B19" s="199"/>
+      <c r="C19" s="199"/>
+      <c r="D19" s="199"/>
+      <c r="E19" s="199"/>
+      <c r="F19" s="199"/>
+      <c r="G19" s="199"/>
+      <c r="H19" s="199"/>
+      <c r="I19" s="199"/>
+      <c r="J19" s="199"/>
+      <c r="K19" s="199"/>
       <c r="L19" s="1"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
@@ -22487,15 +22487,15 @@
       </c>
       <c r="D20" s="71"/>
       <c r="E20" s="49"/>
-      <c r="F20" s="188" t="s">
+      <c r="F20" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="189"/>
+      <c r="G20" s="176"/>
       <c r="H20" s="69"/>
-      <c r="I20" s="190" t="s">
+      <c r="I20" s="177" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="190"/>
+      <c r="J20" s="177"/>
       <c r="K20" s="70"/>
       <c r="L20" s="1"/>
       <c r="V20" s="4"/>
@@ -22636,8 +22636,8 @@
         <v>30</v>
       </c>
       <c r="E24" s="50"/>
-      <c r="F24" s="174"/>
-      <c r="G24" s="173"/>
+      <c r="F24" s="165"/>
+      <c r="G24" s="166"/>
       <c r="H24" s="61"/>
       <c r="I24" s="42" t="s">
         <v>56</v>
@@ -22663,11 +22663,11 @@
         <v>31</v>
       </c>
       <c r="E25" s="50"/>
-      <c r="F25" s="174"/>
-      <c r="G25" s="173"/>
+      <c r="F25" s="165"/>
+      <c r="G25" s="166"/>
       <c r="H25" s="61"/>
-      <c r="I25" s="174"/>
-      <c r="J25" s="175"/>
+      <c r="I25" s="165"/>
+      <c r="J25" s="192"/>
       <c r="K25" s="58"/>
       <c r="L25" s="1"/>
     </row>
@@ -22677,31 +22677,31 @@
       <c r="C26" s="139"/>
       <c r="D26" s="104"/>
       <c r="E26" s="79"/>
-      <c r="F26" s="194"/>
-      <c r="G26" s="195"/>
+      <c r="F26" s="178"/>
+      <c r="G26" s="179"/>
       <c r="H26" s="80"/>
-      <c r="I26" s="194"/>
-      <c r="J26" s="196"/>
+      <c r="I26" s="178"/>
+      <c r="J26" s="180"/>
       <c r="K26" s="81"/>
       <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
-      <c r="A27" s="183" t="s">
+      <c r="A27" s="167" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="184"/>
-      <c r="C27" s="184"/>
-      <c r="D27" s="185"/>
+      <c r="B27" s="168"/>
+      <c r="C27" s="168"/>
+      <c r="D27" s="169"/>
       <c r="E27" s="68"/>
-      <c r="F27" s="192" t="s">
+      <c r="F27" s="200" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="193"/>
+      <c r="G27" s="201"/>
       <c r="H27" s="69"/>
-      <c r="I27" s="177" t="s">
+      <c r="I27" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="J27" s="178"/>
+      <c r="J27" s="194"/>
       <c r="K27" s="70"/>
       <c r="L27" s="1"/>
     </row>
@@ -22715,10 +22715,10 @@
       </c>
       <c r="D28" s="108"/>
       <c r="E28" s="84"/>
-      <c r="F28" s="179" t="s">
+      <c r="F28" s="195" t="s">
         <v>41</v>
       </c>
-      <c r="G28" s="180"/>
+      <c r="G28" s="196"/>
       <c r="H28" s="65" t="s">
         <v>16</v>
       </c>
@@ -22747,8 +22747,8 @@
         <v>21</v>
       </c>
       <c r="E29" s="51"/>
-      <c r="F29" s="179"/>
-      <c r="G29" s="180"/>
+      <c r="F29" s="195"/>
+      <c r="G29" s="196"/>
       <c r="H29" s="57" t="s">
         <v>17</v>
       </c>
@@ -22775,8 +22775,8 @@
       </c>
       <c r="D30" s="74"/>
       <c r="E30" s="51"/>
-      <c r="F30" s="179"/>
-      <c r="G30" s="180"/>
+      <c r="F30" s="195"/>
+      <c r="G30" s="196"/>
       <c r="H30" s="57" t="s">
         <v>9</v>
       </c>
@@ -22805,8 +22805,8 @@
         <v>8</v>
       </c>
       <c r="E31" s="51"/>
-      <c r="F31" s="179"/>
-      <c r="G31" s="180"/>
+      <c r="F31" s="195"/>
+      <c r="G31" s="196"/>
       <c r="H31" s="57" t="s">
         <v>19</v>
       </c>
@@ -22831,8 +22831,8 @@
       </c>
       <c r="D32" s="75"/>
       <c r="E32" s="52"/>
-      <c r="F32" s="181"/>
-      <c r="G32" s="182"/>
+      <c r="F32" s="197"/>
+      <c r="G32" s="198"/>
       <c r="H32" s="62"/>
       <c r="I32" s="48"/>
       <c r="J32" s="36"/>
@@ -22959,8 +22959,8 @@
         <f>C13*C13</f>
         <v>2.25</v>
       </c>
-      <c r="H6" s="186"/>
-      <c r="J6" s="187">
+      <c r="H6" s="170"/>
+      <c r="J6" s="171">
         <f>G6+G7</f>
         <v>3.69</v>
       </c>
@@ -22970,8 +22970,8 @@
         <f>G6</f>
         <v>2.25</v>
       </c>
-      <c r="O6" s="186"/>
-      <c r="Q6" s="187">
+      <c r="O6" s="170"/>
+      <c r="Q6" s="171">
         <f>N6+N7</f>
         <v>5.13</v>
       </c>
@@ -22984,18 +22984,18 @@
         <f>C14*C14</f>
         <v>1.44</v>
       </c>
-      <c r="H7" s="186"/>
+      <c r="H7" s="170"/>
       <c r="I7" s="19"/>
-      <c r="J7" s="187"/>
+      <c r="J7" s="171"/>
       <c r="K7" s="19"/>
       <c r="M7" s="15"/>
       <c r="N7" s="41">
         <f>2*G7</f>
         <v>2.88</v>
       </c>
-      <c r="O7" s="186"/>
+      <c r="O7" s="170"/>
       <c r="P7" s="19"/>
-      <c r="Q7" s="187"/>
+      <c r="Q7" s="171"/>
       <c r="R7" s="19"/>
     </row>
     <row r="8" spans="2:18" s="4" customFormat="1" x14ac:dyDescent="0.75">
@@ -23177,19 +23177,19 @@
       <c r="X18" s="4"/>
     </row>
     <row r="19" spans="1:25" ht="39" thickBot="1" x14ac:dyDescent="1.1000000000000001">
-      <c r="A19" s="191" t="s">
+      <c r="A19" s="199" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="191"/>
-      <c r="C19" s="191"/>
-      <c r="D19" s="191"/>
-      <c r="E19" s="191"/>
-      <c r="F19" s="191"/>
-      <c r="G19" s="191"/>
-      <c r="H19" s="191"/>
-      <c r="I19" s="191"/>
-      <c r="J19" s="191"/>
-      <c r="K19" s="191"/>
+      <c r="B19" s="199"/>
+      <c r="C19" s="199"/>
+      <c r="D19" s="199"/>
+      <c r="E19" s="199"/>
+      <c r="F19" s="199"/>
+      <c r="G19" s="199"/>
+      <c r="H19" s="199"/>
+      <c r="I19" s="199"/>
+      <c r="J19" s="199"/>
+      <c r="K19" s="199"/>
       <c r="L19" s="1"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
@@ -23206,15 +23206,15 @@
       </c>
       <c r="D20" s="71"/>
       <c r="E20" s="49"/>
-      <c r="F20" s="188" t="s">
+      <c r="F20" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="189"/>
+      <c r="G20" s="176"/>
       <c r="H20" s="69"/>
-      <c r="I20" s="190" t="s">
+      <c r="I20" s="177" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="190"/>
+      <c r="J20" s="177"/>
       <c r="K20" s="70"/>
       <c r="L20" s="1"/>
       <c r="V20" s="4"/>
@@ -23356,8 +23356,8 @@
         <v>4</v>
       </c>
       <c r="E24" s="50"/>
-      <c r="F24" s="174"/>
-      <c r="G24" s="173"/>
+      <c r="F24" s="165"/>
+      <c r="G24" s="166"/>
       <c r="H24" s="61"/>
       <c r="I24" s="42" t="s">
         <v>56</v>
@@ -23383,11 +23383,11 @@
         <v>30</v>
       </c>
       <c r="E25" s="50"/>
-      <c r="F25" s="174"/>
-      <c r="G25" s="173"/>
+      <c r="F25" s="165"/>
+      <c r="G25" s="166"/>
       <c r="H25" s="61"/>
-      <c r="I25" s="174"/>
-      <c r="J25" s="175"/>
+      <c r="I25" s="165"/>
+      <c r="J25" s="192"/>
       <c r="K25" s="58"/>
       <c r="L25" s="1"/>
     </row>
@@ -23405,31 +23405,31 @@
         <v>31</v>
       </c>
       <c r="E26" s="79"/>
-      <c r="F26" s="194"/>
-      <c r="G26" s="195"/>
+      <c r="F26" s="178"/>
+      <c r="G26" s="179"/>
       <c r="H26" s="80"/>
-      <c r="I26" s="194"/>
-      <c r="J26" s="196"/>
+      <c r="I26" s="178"/>
+      <c r="J26" s="180"/>
       <c r="K26" s="81"/>
       <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
-      <c r="A27" s="183" t="s">
+      <c r="A27" s="167" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="184"/>
-      <c r="C27" s="184"/>
-      <c r="D27" s="185"/>
+      <c r="B27" s="168"/>
+      <c r="C27" s="168"/>
+      <c r="D27" s="169"/>
       <c r="E27" s="68"/>
-      <c r="F27" s="177" t="s">
+      <c r="F27" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="169"/>
+      <c r="G27" s="182"/>
       <c r="H27" s="69"/>
-      <c r="I27" s="177" t="s">
+      <c r="I27" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="J27" s="178"/>
+      <c r="J27" s="194"/>
       <c r="K27" s="70"/>
       <c r="L27" s="1"/>
     </row>
@@ -23733,10 +23733,10 @@
         <f>POWER(G5,2)</f>
         <v>0.48008269440000007</v>
       </c>
-      <c r="H8" s="186"/>
-      <c r="J8" s="187">
+      <c r="H8" s="170"/>
+      <c r="J8" s="171">
         <f>G8+G9</f>
-        <v>8.8076934720000022</v>
+        <v>5.2888053888000011</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="19"/>
@@ -23746,11 +23746,11 @@
       <c r="E9" s="43"/>
       <c r="F9" s="15"/>
       <c r="G9" s="41">
-        <f>POWER(G5+G6,2)</f>
-        <v>8.3276107776000021</v>
-      </c>
-      <c r="H9" s="186"/>
-      <c r="J9" s="187"/>
+        <f>POWER(G6,2)</f>
+        <v>4.808722694400001</v>
+      </c>
+      <c r="H9" s="170"/>
+      <c r="J9" s="171"/>
     </row>
     <row r="10" spans="2:13" s="19" customFormat="1" x14ac:dyDescent="0.75">
       <c r="E10" s="43"/>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="G13" s="40">
         <f>J8-G11</f>
-        <v>10.327096166400002</v>
+        <v>6.8082080832000011</v>
       </c>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
@@ -23841,7 +23841,7 @@
       <c r="F16" s="15"/>
       <c r="G16" s="97">
         <f>SQRT(G13)</f>
-        <v>3.213579961102571</v>
+        <v>2.609254315546877</v>
       </c>
       <c r="H16" s="22"/>
       <c r="I16" s="15"/>
@@ -23876,19 +23876,19 @@
       <c r="X18" s="4"/>
     </row>
     <row r="19" spans="1:25" ht="39" thickBot="1" x14ac:dyDescent="1.1000000000000001">
-      <c r="A19" s="197" t="s">
+      <c r="A19" s="172" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="198"/>
-      <c r="C19" s="198"/>
-      <c r="D19" s="198"/>
-      <c r="E19" s="198"/>
-      <c r="F19" s="198"/>
-      <c r="G19" s="198"/>
-      <c r="H19" s="198"/>
-      <c r="I19" s="198"/>
-      <c r="J19" s="198"/>
-      <c r="K19" s="199"/>
+      <c r="B19" s="173"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="173"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="173"/>
+      <c r="H19" s="173"/>
+      <c r="I19" s="173"/>
+      <c r="J19" s="173"/>
+      <c r="K19" s="174"/>
       <c r="L19" s="1"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
@@ -23905,15 +23905,15 @@
       </c>
       <c r="D20" s="71"/>
       <c r="E20" s="70"/>
-      <c r="F20" s="188" t="s">
+      <c r="F20" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="189"/>
+      <c r="G20" s="176"/>
       <c r="H20" s="69"/>
-      <c r="I20" s="190" t="s">
+      <c r="I20" s="177" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="190"/>
+      <c r="J20" s="177"/>
       <c r="K20" s="70"/>
       <c r="L20" s="1"/>
       <c r="V20" s="4"/>
@@ -23952,7 +23952,7 @@
       </c>
       <c r="J21" s="96">
         <f>$C$22</f>
-        <v>3.213579961102571</v>
+        <v>2.609254315546877</v>
       </c>
       <c r="K21" s="65" t="s">
         <v>16</v>
@@ -23972,7 +23972,7 @@
       </c>
       <c r="C22" s="141">
         <f>G16</f>
-        <v>3.213579961102571</v>
+        <v>2.609254315546877</v>
       </c>
       <c r="D22" s="103" t="s">
         <v>22</v>
@@ -23995,7 +23995,7 @@
       </c>
       <c r="J22" s="27">
         <f>(J21+($C$24*$C$25))/$C$25</f>
-        <v>7.3635799611025714</v>
+        <v>6.7592543155468778</v>
       </c>
       <c r="K22" s="57" t="s">
         <v>17</v>
@@ -24027,7 +24027,7 @@
       </c>
       <c r="G23" s="46">
         <f>$C$28-G22</f>
-        <v>72.849999999999994</v>
+        <v>60.85</v>
       </c>
       <c r="H23" s="57" t="s">
         <v>9</v>
@@ -24037,7 +24037,7 @@
       </c>
       <c r="J23" s="56">
         <f>J22-$C$21</f>
-        <v>0.8635799611025714</v>
+        <v>0.25925431554687783</v>
       </c>
       <c r="K23" s="57" t="s">
         <v>9</v>
@@ -24060,8 +24060,8 @@
         <v>30</v>
       </c>
       <c r="E24" s="58"/>
-      <c r="F24" s="174"/>
-      <c r="G24" s="173"/>
+      <c r="F24" s="165"/>
+      <c r="G24" s="166"/>
       <c r="H24" s="57" t="s">
         <v>19</v>
       </c>
@@ -24070,7 +24070,7 @@
       </c>
       <c r="J24" s="28">
         <f>$C$28-J23</f>
-        <v>71.136420038897427</v>
+        <v>59.740745684453124</v>
       </c>
       <c r="K24" s="58"/>
       <c r="L24" s="1"/>
@@ -24089,8 +24089,8 @@
         <v>31</v>
       </c>
       <c r="E25" s="59"/>
-      <c r="F25" s="174"/>
-      <c r="G25" s="173"/>
+      <c r="F25" s="165"/>
+      <c r="G25" s="166"/>
       <c r="H25" s="62"/>
       <c r="I25" s="48"/>
       <c r="J25" s="36"/>
@@ -24103,29 +24103,29 @@
       <c r="C26" s="139"/>
       <c r="D26" s="104"/>
       <c r="E26" s="81"/>
-      <c r="F26" s="194"/>
-      <c r="G26" s="195"/>
+      <c r="F26" s="178"/>
+      <c r="G26" s="179"/>
       <c r="H26" s="80"/>
-      <c r="I26" s="194"/>
-      <c r="J26" s="196"/>
+      <c r="I26" s="178"/>
+      <c r="J26" s="180"/>
       <c r="K26" s="81"/>
       <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:25" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
-      <c r="A27" s="183" t="s">
+      <c r="A27" s="167" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="184"/>
-      <c r="C27" s="184"/>
-      <c r="D27" s="185"/>
+      <c r="B27" s="168"/>
+      <c r="C27" s="168"/>
+      <c r="D27" s="169"/>
       <c r="E27" s="70"/>
-      <c r="F27" s="177" t="s">
+      <c r="F27" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="169"/>
+      <c r="G27" s="182"/>
       <c r="H27" s="69"/>
-      <c r="I27" s="200"/>
-      <c r="J27" s="201"/>
+      <c r="I27" s="183"/>
+      <c r="J27" s="184"/>
       <c r="K27" s="70"/>
       <c r="L27" s="1"/>
     </row>
@@ -24135,7 +24135,7 @@
         <v>5</v>
       </c>
       <c r="C28" s="110">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D28" s="108"/>
       <c r="E28" s="65" t="s">
@@ -24146,7 +24146,7 @@
       </c>
       <c r="G28" s="96">
         <f>$C$22</f>
-        <v>3.213579961102571</v>
+        <v>2.609254315546877</v>
       </c>
       <c r="H28" s="148" t="s">
         <v>16</v>
@@ -24176,7 +24176,7 @@
       </c>
       <c r="G29" s="27">
         <f>(G28+($C$24*$C$25))/$C$25</f>
-        <v>7.3635799611025714</v>
+        <v>6.7592543155468778</v>
       </c>
       <c r="H29" s="149" t="s">
         <v>17</v>
@@ -24193,7 +24193,7 @@
       </c>
       <c r="C30" s="10">
         <f>J23</f>
-        <v>0.8635799611025714</v>
+        <v>0.25925431554687783</v>
       </c>
       <c r="D30" s="74"/>
       <c r="E30" s="57" t="s">
@@ -24204,7 +24204,7 @@
       </c>
       <c r="G30" s="56">
         <f>G29-$C$21</f>
-        <v>0.8635799611025714</v>
+        <v>0.25925431554687783</v>
       </c>
       <c r="H30" s="149" t="s">
         <v>9</v>
@@ -24221,7 +24221,7 @@
       </c>
       <c r="C31" s="10">
         <f>G31</f>
-        <v>71.136420038897427</v>
+        <v>59.740745684453124</v>
       </c>
       <c r="D31" s="74" t="s">
         <v>8</v>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="G31" s="28">
         <f>$C$28-G30</f>
-        <v>71.136420038897427</v>
+        <v>59.740745684453124</v>
       </c>
       <c r="H31" s="150"/>
       <c r="I31" s="157"/>

--- a/สูตรคำนวน ANT_สามเหลี่ยม.xlsx
+++ b/สูตรคำนวน ANT_สามเหลี่ยม.xlsx
@@ -2009,6 +2009,21 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2018,25 +2033,10 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -21781,19 +21781,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="55.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="185" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="185"/>
+      <c r="K1" s="185"/>
     </row>
     <row r="2" spans="1:23" s="2" customFormat="1" ht="30.6" thickBot="1" x14ac:dyDescent="0.8">
       <c r="A2" s="89"/>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="D2" s="92"/>
       <c r="E2" s="88"/>
-      <c r="F2" s="188" t="s">
+      <c r="F2" s="187" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="182"/>
@@ -21813,7 +21813,7 @@
       <c r="I2" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="194"/>
+      <c r="J2" s="188"/>
       <c r="K2" s="94"/>
     </row>
     <row r="3" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
@@ -21937,7 +21937,7 @@
         <v>30</v>
       </c>
       <c r="E6" s="37"/>
-      <c r="F6" s="191"/>
+      <c r="F6" s="186"/>
       <c r="G6" s="166"/>
       <c r="H6" s="61"/>
       <c r="I6" s="42" t="s">
@@ -21963,11 +21963,11 @@
         <v>31</v>
       </c>
       <c r="E7" s="37"/>
-      <c r="F7" s="191"/>
+      <c r="F7" s="186"/>
       <c r="G7" s="166"/>
       <c r="H7" s="61"/>
       <c r="I7" s="165"/>
-      <c r="J7" s="192"/>
+      <c r="J7" s="189"/>
       <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
@@ -21984,30 +21984,30 @@
         <v>6</v>
       </c>
       <c r="E8" s="37"/>
-      <c r="F8" s="191"/>
+      <c r="F8" s="186"/>
       <c r="G8" s="166"/>
       <c r="H8" s="61"/>
       <c r="I8" s="165"/>
-      <c r="J8" s="192"/>
+      <c r="J8" s="189"/>
       <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
-      <c r="A9" s="185" t="s">
+      <c r="A9" s="190" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="186"/>
-      <c r="C9" s="186"/>
-      <c r="D9" s="187"/>
+      <c r="B9" s="191"/>
+      <c r="C9" s="191"/>
+      <c r="D9" s="192"/>
       <c r="E9" s="88"/>
-      <c r="F9" s="188" t="s">
+      <c r="F9" s="187" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="182"/>
       <c r="H9" s="69"/>
-      <c r="I9" s="189" t="s">
+      <c r="I9" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="190"/>
+      <c r="J9" s="194"/>
       <c r="K9" s="70"/>
     </row>
     <row r="10" spans="1:23" ht="27.6" thickBot="1" x14ac:dyDescent="0.8">
@@ -22244,17 +22244,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="I8:J8"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="I8:J8"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" scale="55" orientation="landscape" r:id="rId1"/>
@@ -22667,7 +22667,7 @@
       <c r="G25" s="166"/>
       <c r="H25" s="61"/>
       <c r="I25" s="165"/>
-      <c r="J25" s="192"/>
+      <c r="J25" s="189"/>
       <c r="K25" s="58"/>
       <c r="L25" s="1"/>
     </row>
@@ -22701,7 +22701,7 @@
       <c r="I27" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="J27" s="194"/>
+      <c r="J27" s="188"/>
       <c r="K27" s="70"/>
       <c r="L27" s="1"/>
     </row>
@@ -23387,7 +23387,7 @@
       <c r="G25" s="166"/>
       <c r="H25" s="61"/>
       <c r="I25" s="165"/>
-      <c r="J25" s="192"/>
+      <c r="J25" s="189"/>
       <c r="K25" s="58"/>
       <c r="L25" s="1"/>
     </row>
@@ -23429,7 +23429,7 @@
       <c r="I27" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="J27" s="194"/>
+      <c r="J27" s="188"/>
       <c r="K27" s="70"/>
       <c r="L27" s="1"/>
     </row>
@@ -23630,6 +23630,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="I26:J26"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="I27:J27"/>
@@ -23639,12 +23645,6 @@
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="F24:G24"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="I26:J26"/>
   </mergeCells>
   <pageMargins left="0.37" right="0.17" top="0.37" bottom="0.17" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="42" orientation="landscape" r:id="rId1"/>
